--- a/research/traditional_assets/database/data/poland/poland_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_electronics_consumer_office.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1059631689278575</v>
+        <v>0.1057982889068946</v>
       </c>
       <c r="C2">
-        <v>3.814714501829543</v>
+        <v>3.782255987440077</v>
       </c>
       <c r="D2">
-        <v>3.814714501829543</v>
+        <v>3.820455987440076</v>
       </c>
       <c r="E2">
-        <v>-0.16</v>
+        <v>-0.1218</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1439,28 +1439,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00192146</v>
       </c>
       <c r="N2">
-        <v>0.1029999999999999</v>
+        <v>0.1010785399999999</v>
       </c>
       <c r="O2">
-        <v>0.01956999999999998</v>
+        <v>0.01920492259999998</v>
       </c>
       <c r="P2">
-        <v>0.08342999999999989</v>
+        <v>0.08187361739999989</v>
       </c>
       <c r="Q2">
-        <v>0.7524299999999999</v>
+        <v>0.7508736173999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1059631689278575</v>
+        <v>0.1064554130372672</v>
       </c>
       <c r="T2">
-        <v>1.101909567345926</v>
+        <v>1.110925191078756</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>53.60507114381765</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1057982889068946</v>
+        <v>0.1056334088859316</v>
       </c>
       <c r="C3">
-        <v>3.782255987440077</v>
+        <v>3.749814781998127</v>
       </c>
       <c r="D3">
-        <v>3.820455987440076</v>
+        <v>3.826214781998127</v>
       </c>
       <c r="E3">
-        <v>-0.1218</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="F3">
-        <v>0.0382</v>
+        <v>0.07640000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M3">
-        <v>0.00192146</v>
+        <v>0.00384292</v>
       </c>
       <c r="N3">
-        <v>0.1010785399999999</v>
+        <v>0.09915707999999987</v>
       </c>
       <c r="O3">
-        <v>0.01920492259999998</v>
+        <v>0.01883984519999998</v>
       </c>
       <c r="P3">
-        <v>0.08187361739999989</v>
+        <v>0.08031723479999989</v>
       </c>
       <c r="Q3">
-        <v>0.7508736173999999</v>
+        <v>0.7493172347999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1064554130372672</v>
+        <v>0.1069577029448282</v>
       </c>
       <c r="T3">
-        <v>1.110925191078756</v>
+        <v>1.120124807132665</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>53.60507114381765</v>
+        <v>26.80253557190883</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1056334088859316</v>
+        <v>0.1054685288649687</v>
       </c>
       <c r="C4">
-        <v>3.749814781998127</v>
+        <v>3.717390963894194</v>
       </c>
       <c r="D4">
-        <v>3.826214781998127</v>
+        <v>3.831990963894194</v>
       </c>
       <c r="E4">
-        <v>-0.08359999999999999</v>
+        <v>-0.0454</v>
       </c>
       <c r="F4">
-        <v>0.07640000000000001</v>
+        <v>0.1146</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1603,28 +1603,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M4">
-        <v>0.00384292</v>
+        <v>0.00576438</v>
       </c>
       <c r="N4">
-        <v>0.09915707999999987</v>
+        <v>0.09723561999999987</v>
       </c>
       <c r="O4">
-        <v>0.01883984519999998</v>
+        <v>0.01847476779999998</v>
       </c>
       <c r="P4">
-        <v>0.08031723479999989</v>
+        <v>0.0787608521999999</v>
       </c>
       <c r="Q4">
-        <v>0.7493172347999999</v>
+        <v>0.7477608521999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1069577029448282</v>
+        <v>0.1074703493453286</v>
       </c>
       <c r="T4">
-        <v>1.120124807132665</v>
+        <v>1.129514105991808</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>26.80253557190883</v>
+        <v>17.86835704793922</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1054685288649687</v>
+        <v>0.1053036488440058</v>
       </c>
       <c r="C5">
-        <v>3.717390963894194</v>
+        <v>3.684984611992857</v>
       </c>
       <c r="D5">
-        <v>3.831990963894194</v>
+        <v>3.837784611992857</v>
       </c>
       <c r="E5">
-        <v>-0.0454</v>
+        <v>-0.007199999999999984</v>
       </c>
       <c r="F5">
-        <v>0.1146</v>
+        <v>0.1528</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M5">
-        <v>0.00576438</v>
+        <v>0.00768584</v>
       </c>
       <c r="N5">
-        <v>0.09723561999999987</v>
+        <v>0.09531415999999987</v>
       </c>
       <c r="O5">
-        <v>0.01847476779999998</v>
+        <v>0.01810969039999998</v>
       </c>
       <c r="P5">
-        <v>0.0787608521999999</v>
+        <v>0.07720446959999989</v>
       </c>
       <c r="Q5">
-        <v>0.7477608521999999</v>
+        <v>0.7462044696</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1074703493453286</v>
+        <v>0.1079936758791727</v>
       </c>
       <c r="T5">
-        <v>1.129514105991808</v>
+        <v>1.139099015243851</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>17.86835704793922</v>
+        <v>13.40126778595441</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1053036488440058</v>
+        <v>0.1051995188230428</v>
       </c>
       <c r="C6">
-        <v>3.684984611992857</v>
+        <v>3.650452626462911</v>
       </c>
       <c r="D6">
-        <v>3.837784611992857</v>
+        <v>3.841452626462911</v>
       </c>
       <c r="E6">
-        <v>-0.007199999999999984</v>
+        <v>0.03100000000000003</v>
       </c>
       <c r="F6">
-        <v>0.1528</v>
+        <v>0.191</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1767,45 +1767,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M6">
-        <v>0.00768584</v>
+        <v>0.009893800000000001</v>
       </c>
       <c r="N6">
-        <v>0.09531415999999987</v>
+        <v>0.09310619999999986</v>
       </c>
       <c r="O6">
-        <v>0.01810969039999998</v>
+        <v>0.01769017799999997</v>
       </c>
       <c r="P6">
-        <v>0.07720446959999989</v>
+        <v>0.07541602199999989</v>
       </c>
       <c r="Q6">
-        <v>0.7462044696</v>
+        <v>0.7444160219999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1079936758791727</v>
+        <v>0.1085280198137293</v>
       </c>
       <c r="T6">
-        <v>1.139099015243851</v>
+        <v>1.148885712059094</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.19</v>
       </c>
       <c r="W6">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.40126778595441</v>
+        <v>10.41056014878003</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1051995188230428</v>
+        <v>0.1051294088020799</v>
       </c>
       <c r="C7">
-        <v>3.650452626462911</v>
+        <v>3.61472622735196</v>
       </c>
       <c r="D7">
-        <v>3.841452626462911</v>
+        <v>3.84392622735196</v>
       </c>
       <c r="E7">
-        <v>0.03100000000000003</v>
+        <v>0.06920000000000004</v>
       </c>
       <c r="F7">
-        <v>0.191</v>
+        <v>0.2292</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1849,45 +1849,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M7">
-        <v>0.009893800000000001</v>
+        <v>0.0122622</v>
       </c>
       <c r="N7">
-        <v>0.09310619999999986</v>
+        <v>0.09073779999999987</v>
       </c>
       <c r="O7">
-        <v>0.01769017799999997</v>
+        <v>0.01724018199999998</v>
       </c>
       <c r="P7">
-        <v>0.07541602199999989</v>
+        <v>0.07349761799999989</v>
       </c>
       <c r="Q7">
-        <v>0.7444160219999999</v>
+        <v>0.7424976179999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1085280198137293</v>
+        <v>0.1090737327681701</v>
       </c>
       <c r="T7">
-        <v>1.148885712059094</v>
+        <v>1.158880636466151</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.19</v>
       </c>
       <c r="W7">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.41056014878003</v>
+        <v>8.399797752442453</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1051294088020799</v>
+        <v>0.105035808781117</v>
       </c>
       <c r="C8">
-        <v>3.61472622735196</v>
+        <v>3.579833565107637</v>
       </c>
       <c r="D8">
-        <v>3.84392622735196</v>
+        <v>3.847233565107637</v>
       </c>
       <c r="E8">
-        <v>0.06920000000000001</v>
+        <v>0.1074</v>
       </c>
       <c r="F8">
-        <v>0.2292</v>
+        <v>0.2674</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1931,45 +1931,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M8">
-        <v>0.0122622</v>
+        <v>0.01451982</v>
       </c>
       <c r="N8">
-        <v>0.09073779999999987</v>
+        <v>0.08848017999999987</v>
       </c>
       <c r="O8">
-        <v>0.01724018199999998</v>
+        <v>0.01681123419999998</v>
       </c>
       <c r="P8">
-        <v>0.07349761799999989</v>
+        <v>0.07166894579999988</v>
       </c>
       <c r="Q8">
-        <v>0.7424976179999999</v>
+        <v>0.7406689458</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1090737327681701</v>
+        <v>0.109631181485072</v>
       </c>
       <c r="T8">
-        <v>1.158880636466151</v>
+        <v>1.169090505484113</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.19</v>
       </c>
       <c r="W8">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.399797752442455</v>
+        <v>7.093751850918253</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.105035808781117</v>
+        <v>0.1049033287601541</v>
       </c>
       <c r="C9">
-        <v>3.579833565107638</v>
+        <v>3.546324460069366</v>
       </c>
       <c r="D9">
-        <v>3.847233565107638</v>
+        <v>3.851924460069366</v>
       </c>
       <c r="E9">
-        <v>0.1074</v>
+        <v>0.1456</v>
       </c>
       <c r="F9">
-        <v>0.2674</v>
+        <v>0.3056</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2013,28 +2013,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M9">
-        <v>0.01451982</v>
+        <v>0.01659408</v>
       </c>
       <c r="N9">
-        <v>0.08848017999999987</v>
+        <v>0.08640591999999986</v>
       </c>
       <c r="O9">
-        <v>0.01681123419999998</v>
+        <v>0.01641712479999997</v>
       </c>
       <c r="P9">
-        <v>0.07166894579999988</v>
+        <v>0.06998879519999988</v>
       </c>
       <c r="Q9">
-        <v>0.7406689458</v>
+        <v>0.7389887951999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.109631181485072</v>
+        <v>0.1102007486523414</v>
       </c>
       <c r="T9">
-        <v>1.169090505484113</v>
+        <v>1.179522328176378</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.093751850918252</v>
+        <v>6.207032869553469</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1049033287601541</v>
+        <v>0.1048437487391911</v>
       </c>
       <c r="C10">
-        <v>3.546324460069366</v>
+        <v>3.510237819620148</v>
       </c>
       <c r="D10">
-        <v>3.851924460069366</v>
+        <v>3.854037819620148</v>
       </c>
       <c r="E10">
-        <v>0.1456</v>
+        <v>0.1838</v>
       </c>
       <c r="F10">
-        <v>0.3056</v>
+        <v>0.3438</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2095,45 +2095,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M10">
-        <v>0.01659408</v>
+        <v>0.01901214</v>
       </c>
       <c r="N10">
-        <v>0.08640591999999986</v>
+        <v>0.08398785999999987</v>
       </c>
       <c r="O10">
-        <v>0.01641712479999997</v>
+        <v>0.01595769339999998</v>
       </c>
       <c r="P10">
-        <v>0.06998879519999988</v>
+        <v>0.0680301665999999</v>
       </c>
       <c r="Q10">
-        <v>0.7389887951999999</v>
+        <v>0.7370301666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1102007486523414</v>
+        <v>0.1107828337793309</v>
       </c>
       <c r="T10">
-        <v>1.179522328176378</v>
+        <v>1.190183421697044</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.19</v>
       </c>
       <c r="W10">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.207032869553469</v>
+        <v>5.417591076017738</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1048437487391911</v>
+        <v>0.1047193687182282</v>
       </c>
       <c r="C11">
-        <v>3.510237819620148</v>
+        <v>3.476457178679095</v>
       </c>
       <c r="D11">
-        <v>3.854037819620148</v>
+        <v>3.858457178679096</v>
       </c>
       <c r="E11">
-        <v>0.1838</v>
+        <v>0.222</v>
       </c>
       <c r="F11">
-        <v>0.3438</v>
+        <v>0.382</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2177,28 +2177,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M11">
-        <v>0.01901214</v>
+        <v>0.0211246</v>
       </c>
       <c r="N11">
-        <v>0.08398785999999987</v>
+        <v>0.08187539999999988</v>
       </c>
       <c r="O11">
-        <v>0.01595769339999998</v>
+        <v>0.01555632599999998</v>
       </c>
       <c r="P11">
-        <v>0.0680301665999999</v>
+        <v>0.06631907399999989</v>
       </c>
       <c r="Q11">
-        <v>0.7370301666</v>
+        <v>0.735319074</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1107828337793309</v>
+        <v>0.1113778541313647</v>
       </c>
       <c r="T11">
-        <v>1.190183421697044</v>
+        <v>1.201081428407059</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.417591076017738</v>
+        <v>4.875831968415964</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1047193687182282</v>
+        <v>0.1048177386972653</v>
       </c>
       <c r="C12">
-        <v>3.476457178679095</v>
+        <v>3.434761147682667</v>
       </c>
       <c r="D12">
-        <v>3.858457178679096</v>
+        <v>3.854961147682667</v>
       </c>
       <c r="E12">
-        <v>0.2220000000000001</v>
+        <v>0.2602</v>
       </c>
       <c r="F12">
-        <v>0.3820000000000001</v>
+        <v>0.4202</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2259,45 +2259,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M12">
-        <v>0.0211246</v>
+        <v>0.02428756</v>
       </c>
       <c r="N12">
-        <v>0.08187539999999986</v>
+        <v>0.07871243999999987</v>
       </c>
       <c r="O12">
-        <v>0.01555632599999997</v>
+        <v>0.01495536359999998</v>
       </c>
       <c r="P12">
-        <v>0.06631907399999989</v>
+        <v>0.06375707639999989</v>
       </c>
       <c r="Q12">
-        <v>0.735319074</v>
+        <v>0.7327570764</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1113778541313647</v>
+        <v>0.1119862457272643</v>
       </c>
       <c r="T12">
-        <v>1.201081428407059</v>
+        <v>1.212224334144265</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.875831968415962</v>
+        <v>4.240854165671639</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1048177386972653</v>
+        <v>0.1050538086763023</v>
       </c>
       <c r="C13">
-        <v>3.434761147682667</v>
+        <v>3.388197100534941</v>
       </c>
       <c r="D13">
-        <v>3.854961147682667</v>
+        <v>3.846597100534941</v>
       </c>
       <c r="E13">
-        <v>0.2602</v>
+        <v>0.2984</v>
       </c>
       <c r="F13">
-        <v>0.4202</v>
+        <v>0.4584</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2341,45 +2341,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M13">
-        <v>0.02428756</v>
+        <v>0.02809992</v>
       </c>
       <c r="N13">
-        <v>0.07871243999999987</v>
+        <v>0.07490007999999987</v>
       </c>
       <c r="O13">
-        <v>0.01495536359999998</v>
+        <v>0.01423101519999997</v>
       </c>
       <c r="P13">
-        <v>0.06375707639999989</v>
+        <v>0.06066906479999989</v>
       </c>
       <c r="Q13">
-        <v>0.7327570764</v>
+        <v>0.7296690647999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1119862457272643</v>
+        <v>0.112608464404889</v>
       </c>
       <c r="T13">
-        <v>1.212224334144265</v>
+        <v>1.223620487739135</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.240854165671639</v>
+        <v>3.665490862607433</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1050538086763023</v>
+        <v>0.1052728686553394</v>
       </c>
       <c r="C14">
-        <v>3.388197100534941</v>
+        <v>3.342268124860767</v>
       </c>
       <c r="D14">
-        <v>3.846597100534941</v>
+        <v>3.838868124860767</v>
       </c>
       <c r="E14">
-        <v>0.2984</v>
+        <v>0.3366</v>
       </c>
       <c r="F14">
-        <v>0.4584</v>
+        <v>0.4966</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2423,45 +2423,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M14">
-        <v>0.02809992</v>
+        <v>0.03183206</v>
       </c>
       <c r="N14">
-        <v>0.07490007999999987</v>
+        <v>0.07116793999999987</v>
       </c>
       <c r="O14">
-        <v>0.01423101519999997</v>
+        <v>0.01352190859999998</v>
       </c>
       <c r="P14">
-        <v>0.06066906479999989</v>
+        <v>0.05764603139999989</v>
       </c>
       <c r="Q14">
-        <v>0.7296690647999999</v>
+        <v>0.7266460313999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.112608464404889</v>
+        <v>0.1132449869601602</v>
       </c>
       <c r="T14">
-        <v>1.223620487739135</v>
+        <v>1.235278621876416</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.19</v>
       </c>
       <c r="W14">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.665490862607433</v>
+        <v>3.235731523501774</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1052728686553394</v>
+        <v>0.1052197686343765</v>
       </c>
       <c r="C15">
-        <v>3.342268124860767</v>
+        <v>3.305938771081092</v>
       </c>
       <c r="D15">
-        <v>3.838868124860767</v>
+        <v>3.840738771081092</v>
       </c>
       <c r="E15">
-        <v>0.3366</v>
+        <v>0.3748</v>
       </c>
       <c r="F15">
-        <v>0.4966</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M15">
-        <v>0.03183206</v>
+        <v>0.03428068000000001</v>
       </c>
       <c r="N15">
-        <v>0.07116793999999987</v>
+        <v>0.06871931999999986</v>
       </c>
       <c r="O15">
-        <v>0.01352190859999998</v>
+        <v>0.01305667079999997</v>
       </c>
       <c r="P15">
-        <v>0.05764603139999989</v>
+        <v>0.05566264919999989</v>
       </c>
       <c r="Q15">
-        <v>0.7266460313999999</v>
+        <v>0.7246626491999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1132449869601602</v>
+        <v>0.1138963123655541</v>
       </c>
       <c r="T15">
-        <v>1.235278621876416</v>
+        <v>1.247207875412238</v>
       </c>
       <c r="U15">
         <v>0.0641</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.235731523501774</v>
+        <v>3.004607843251646</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1052197686343765</v>
+        <v>0.1061143686134135</v>
       </c>
       <c r="C16">
-        <v>3.305938771081092</v>
+        <v>3.236464543339589</v>
       </c>
       <c r="D16">
-        <v>3.840738771081092</v>
+        <v>3.809464543339589</v>
       </c>
       <c r="E16">
-        <v>0.3748</v>
+        <v>0.4130000000000001</v>
       </c>
       <c r="F16">
-        <v>0.5348000000000001</v>
+        <v>0.5730000000000002</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2587,45 +2587,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M16">
-        <v>0.03428068000000001</v>
+        <v>0.04119870000000002</v>
       </c>
       <c r="N16">
-        <v>0.06871931999999986</v>
+        <v>0.06180129999999985</v>
       </c>
       <c r="O16">
-        <v>0.01305667079999997</v>
+        <v>0.01174224699999997</v>
       </c>
       <c r="P16">
-        <v>0.05566264919999989</v>
+        <v>0.05005905299999988</v>
       </c>
       <c r="Q16">
-        <v>0.7246626491999999</v>
+        <v>0.7190590529999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1138963123655541</v>
+        <v>0.1145629630746042</v>
       </c>
       <c r="T16">
-        <v>1.247207875412238</v>
+        <v>1.25941781726655</v>
       </c>
       <c r="U16">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.004607843251646</v>
+        <v>2.500078885984262</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1061143686134135</v>
+        <v>0.1066298885924506</v>
       </c>
       <c r="C17">
-        <v>3.236464543339589</v>
+        <v>3.180472767765184</v>
       </c>
       <c r="D17">
-        <v>3.809464543339589</v>
+        <v>3.791672767765184</v>
       </c>
       <c r="E17">
-        <v>0.413</v>
+        <v>0.4512</v>
       </c>
       <c r="F17">
-        <v>0.5730000000000001</v>
+        <v>0.6112000000000001</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2669,45 +2669,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M17">
-        <v>0.0411987</v>
+        <v>0.04632896000000001</v>
       </c>
       <c r="N17">
-        <v>0.06180129999999986</v>
+        <v>0.05667103999999986</v>
       </c>
       <c r="O17">
-        <v>0.01174224699999997</v>
+        <v>0.01076749759999997</v>
       </c>
       <c r="P17">
-        <v>0.05005905299999989</v>
+        <v>0.04590354239999989</v>
       </c>
       <c r="Q17">
-        <v>0.7190590529999999</v>
+        <v>0.7149035423999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1145629630746042</v>
+        <v>0.1152454864195841</v>
       </c>
       <c r="T17">
-        <v>1.25941781726655</v>
+        <v>1.271918472022154</v>
       </c>
       <c r="U17">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.500078885984263</v>
+        <v>2.223231430189666</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1066298885924506</v>
+        <v>0.1066715585714877</v>
       </c>
       <c r="C18">
-        <v>3.180472767765184</v>
+        <v>3.140841898138266</v>
       </c>
       <c r="D18">
-        <v>3.791672767765184</v>
+        <v>3.790241898138266</v>
       </c>
       <c r="E18">
-        <v>0.4512</v>
+        <v>0.4894000000000001</v>
       </c>
       <c r="F18">
-        <v>0.6112000000000001</v>
+        <v>0.6494000000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2751,28 +2751,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M18">
-        <v>0.04632896000000001</v>
+        <v>0.04922452000000001</v>
       </c>
       <c r="N18">
-        <v>0.05667103999999986</v>
+        <v>0.05377547999999986</v>
       </c>
       <c r="O18">
-        <v>0.01076749759999997</v>
+        <v>0.01021734119999997</v>
       </c>
       <c r="P18">
-        <v>0.04590354239999989</v>
+        <v>0.04355813879999989</v>
       </c>
       <c r="Q18">
-        <v>0.7149035423999999</v>
+        <v>0.7125581388</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1152454864195841</v>
+        <v>0.1159444561102261</v>
       </c>
       <c r="T18">
-        <v>1.271918472022154</v>
+        <v>1.28472034737428</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.223231430189666</v>
+        <v>2.092453110766745</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1066715585714877</v>
+        <v>0.1087835885505248</v>
       </c>
       <c r="C19">
-        <v>3.140841898138266</v>
+        <v>3.03150668314772</v>
       </c>
       <c r="D19">
-        <v>3.790241898138266</v>
+        <v>3.71910668314772</v>
       </c>
       <c r="E19">
-        <v>0.4894000000000001</v>
+        <v>0.5276000000000001</v>
       </c>
       <c r="F19">
-        <v>0.6494000000000001</v>
+        <v>0.6876000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2833,45 +2833,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M19">
-        <v>0.04922452000000001</v>
+        <v>0.06188400000000001</v>
       </c>
       <c r="N19">
-        <v>0.05377547999999986</v>
+        <v>0.04111599999999986</v>
       </c>
       <c r="O19">
-        <v>0.01021734119999997</v>
+        <v>0.007812039999999974</v>
       </c>
       <c r="P19">
-        <v>0.04355813879999989</v>
+        <v>0.03330395999999989</v>
       </c>
       <c r="Q19">
-        <v>0.7125581388</v>
+        <v>0.7023039599999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1159444561102261</v>
+        <v>0.1166604738421033</v>
       </c>
       <c r="T19">
-        <v>1.28472034737428</v>
+        <v>1.297834463588653</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.19</v>
       </c>
       <c r="W19">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.092453110766745</v>
+        <v>1.664404369465449</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1087835885505248</v>
+        <v>0.1089402785295618</v>
       </c>
       <c r="C20">
-        <v>3.03150668314772</v>
+        <v>2.98813546073811</v>
       </c>
       <c r="D20">
-        <v>3.71910668314772</v>
+        <v>3.71393546073811</v>
       </c>
       <c r="E20">
-        <v>0.5276</v>
+        <v>0.5658000000000001</v>
       </c>
       <c r="F20">
-        <v>0.6876</v>
+        <v>0.7258000000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2915,28 +2915,28 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M20">
-        <v>0.06188399999999999</v>
+        <v>0.06532200000000001</v>
       </c>
       <c r="N20">
-        <v>0.04111599999999987</v>
+        <v>0.03767799999999986</v>
       </c>
       <c r="O20">
-        <v>0.007812039999999977</v>
+        <v>0.007158819999999975</v>
       </c>
       <c r="P20">
-        <v>0.0333039599999999</v>
+        <v>0.03051917999999989</v>
       </c>
       <c r="Q20">
-        <v>0.7023039599999999</v>
+        <v>0.6995191799999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1166604738421033</v>
+        <v>0.1173941710241504</v>
       </c>
       <c r="T20">
-        <v>1.297834463588653</v>
+        <v>1.311272385141652</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.66440436946545</v>
+        <v>1.576804139493583</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1089402785295618</v>
+        <v>0.1189405538089541</v>
       </c>
       <c r="C21">
-        <v>2.98813546073811</v>
+        <v>2.647219718378611</v>
       </c>
       <c r="D21">
-        <v>3.71393546073811</v>
+        <v>3.411219718378611</v>
       </c>
       <c r="E21">
-        <v>0.5658000000000001</v>
+        <v>0.6040000000000001</v>
       </c>
       <c r="F21">
-        <v>0.7258000000000001</v>
+        <v>0.7640000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2997,45 +2997,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M21">
-        <v>0.06532200000000001</v>
+        <v>0.1121552</v>
       </c>
       <c r="N21">
-        <v>0.03767799999999986</v>
+        <v>-0.009155200000000155</v>
       </c>
       <c r="O21">
-        <v>0.007158819999999975</v>
+        <v>-0.001739488000000029</v>
       </c>
       <c r="P21">
-        <v>0.03051917999999989</v>
+        <v>-0.007415712000000125</v>
       </c>
       <c r="Q21">
-        <v>0.6995191799999999</v>
+        <v>0.6615842879999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1173941710241504</v>
+        <v>0.118379488072711</v>
       </c>
       <c r="T21">
-        <v>1.311272385141652</v>
+        <v>1.329318812915093</v>
       </c>
       <c r="U21">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.19</v>
+        <v>0.1744903490876925</v>
       </c>
       <c r="W21">
-        <v>0.07290000000000001</v>
+        <v>0.1211848167539267</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.576804139493583</v>
+        <v>0.9183702583562764</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1189405538089541</v>
+        <v>0.1199505538089541</v>
       </c>
       <c r="C22">
-        <v>2.647219718378611</v>
+        <v>2.581167534709957</v>
       </c>
       <c r="D22">
-        <v>3.411219718378611</v>
+        <v>3.383367534709957</v>
       </c>
       <c r="E22">
-        <v>0.6040000000000001</v>
+        <v>0.6422000000000001</v>
       </c>
       <c r="F22">
-        <v>0.7640000000000001</v>
+        <v>0.8022000000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3079,37 +3079,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M22">
-        <v>0.1121552</v>
+        <v>0.11776296</v>
       </c>
       <c r="N22">
-        <v>-0.009155200000000155</v>
+        <v>-0.01476296000000016</v>
       </c>
       <c r="O22">
-        <v>-0.001739488000000029</v>
+        <v>-0.00280496240000003</v>
       </c>
       <c r="P22">
-        <v>-0.007415712000000125</v>
+        <v>-0.01195799760000013</v>
       </c>
       <c r="Q22">
-        <v>0.6615842879999999</v>
+        <v>0.6570420023999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.118379488072711</v>
+        <v>0.1192982157698339</v>
       </c>
       <c r="T22">
-        <v>1.329318812915093</v>
+        <v>1.346145633331739</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.1744903490876925</v>
+        <v>0.1661812848454214</v>
       </c>
       <c r="W22">
-        <v>0.1211848167539267</v>
+        <v>0.1224045873846921</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.9183702583562764</v>
+        <v>0.8746383412916918</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1199505538089541</v>
+        <v>0.1209605538089541</v>
       </c>
       <c r="C23">
-        <v>2.581167534709957</v>
+        <v>2.515566486787927</v>
       </c>
       <c r="D23">
-        <v>3.383367534709957</v>
+        <v>3.355966486787927</v>
       </c>
       <c r="E23">
-        <v>0.6422</v>
+        <v>0.6804</v>
       </c>
       <c r="F23">
-        <v>0.8022</v>
+        <v>0.8404</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3161,37 +3161,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M23">
-        <v>0.11776296</v>
+        <v>0.12337072</v>
       </c>
       <c r="N23">
-        <v>-0.01476296000000014</v>
+        <v>-0.02037072000000015</v>
       </c>
       <c r="O23">
-        <v>-0.002804962400000027</v>
+        <v>-0.003870436800000028</v>
       </c>
       <c r="P23">
-        <v>-0.01195799760000012</v>
+        <v>-0.01650028320000012</v>
       </c>
       <c r="Q23">
-        <v>0.6570420023999999</v>
+        <v>0.6524997168</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1192982157698339</v>
+        <v>0.1202405005873958</v>
       </c>
       <c r="T23">
-        <v>1.346145633331739</v>
+        <v>1.363403910682146</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.1661812848454214</v>
+        <v>0.1586275900797205</v>
       </c>
       <c r="W23">
-        <v>0.1224045873846921</v>
+        <v>0.123513469776297</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8746383412916918</v>
+        <v>0.8348820530511604</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1209605538089541</v>
+        <v>0.1349551814850656</v>
       </c>
       <c r="C24">
-        <v>2.515566486787927</v>
+        <v>2.138767133061768</v>
       </c>
       <c r="D24">
-        <v>3.355966486787927</v>
+        <v>3.017367133061768</v>
       </c>
       <c r="E24">
-        <v>0.6804</v>
+        <v>0.7186000000000001</v>
       </c>
       <c r="F24">
-        <v>0.8404</v>
+        <v>0.8786000000000002</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3243,45 +3243,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M24">
-        <v>0.12337072</v>
+        <v>0.17642288</v>
       </c>
       <c r="N24">
-        <v>-0.02037072000000015</v>
+        <v>-0.07342288000000016</v>
       </c>
       <c r="O24">
-        <v>-0.003870436800000028</v>
+        <v>-0.01395034720000003</v>
       </c>
       <c r="P24">
-        <v>-0.01650028320000012</v>
+        <v>-0.05947253280000013</v>
       </c>
       <c r="Q24">
-        <v>0.6524997168</v>
+        <v>0.6095274672</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1202405005873958</v>
+        <v>0.1219405430315328</v>
       </c>
       <c r="T24">
-        <v>1.363403910682146</v>
+        <v>1.394540785076761</v>
       </c>
       <c r="U24">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1586275900797205</v>
+        <v>0.1109266553181762</v>
       </c>
       <c r="W24">
-        <v>0.123513469776297</v>
+        <v>0.1785259276121102</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8348820530511604</v>
+        <v>0.5838245016746119</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1349551814850656</v>
+        <v>0.1365051814850656</v>
       </c>
       <c r="C25">
-        <v>2.138767133061768</v>
+        <v>2.067221360268533</v>
       </c>
       <c r="D25">
-        <v>3.017367133061768</v>
+        <v>2.984021360268533</v>
       </c>
       <c r="E25">
-        <v>0.7186000000000001</v>
+        <v>0.7568000000000001</v>
       </c>
       <c r="F25">
-        <v>0.8786000000000002</v>
+        <v>0.9168000000000002</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3325,37 +3325,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M25">
-        <v>0.17642288</v>
+        <v>0.1840934400000001</v>
       </c>
       <c r="N25">
-        <v>-0.07342288000000016</v>
+        <v>-0.08109344000000018</v>
       </c>
       <c r="O25">
-        <v>-0.01395034720000003</v>
+        <v>-0.01540775360000004</v>
       </c>
       <c r="P25">
-        <v>-0.05947253280000013</v>
+        <v>-0.06568568640000015</v>
       </c>
       <c r="Q25">
-        <v>0.6095274672</v>
+        <v>0.6033143135999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1219405430315328</v>
+        <v>0.1229423922819477</v>
       </c>
       <c r="T25">
-        <v>1.394540785076761</v>
+        <v>1.412890005933034</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1109266553181762</v>
+        <v>0.1063047113465856</v>
       </c>
       <c r="W25">
-        <v>0.1785259276121102</v>
+        <v>0.1794540139616056</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5838245016746119</v>
+        <v>0.559498480771503</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1365051814850656</v>
+        <v>0.1380551814850656</v>
       </c>
       <c r="C26">
-        <v>2.067221360268533</v>
+        <v>1.996404558438802</v>
       </c>
       <c r="D26">
-        <v>2.984021360268533</v>
+        <v>2.951404558438802</v>
       </c>
       <c r="E26">
-        <v>0.7568</v>
+        <v>0.795</v>
       </c>
       <c r="F26">
-        <v>0.9168000000000001</v>
+        <v>0.9550000000000001</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3407,37 +3407,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M26">
-        <v>0.18409344</v>
+        <v>0.191764</v>
       </c>
       <c r="N26">
-        <v>-0.08109344000000016</v>
+        <v>-0.08876400000000015</v>
       </c>
       <c r="O26">
-        <v>-0.01540775360000003</v>
+        <v>-0.01686516000000003</v>
       </c>
       <c r="P26">
-        <v>-0.06568568640000012</v>
+        <v>-0.07189884000000012</v>
       </c>
       <c r="Q26">
-        <v>0.6033143135999999</v>
+        <v>0.5971011599999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1229423922819477</v>
+        <v>0.1239709575123737</v>
       </c>
       <c r="T26">
-        <v>1.412890005933034</v>
+        <v>1.431728539345475</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1063047113465856</v>
+        <v>0.1020525228927222</v>
       </c>
       <c r="W26">
-        <v>0.1794540139616056</v>
+        <v>0.1803078534031414</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5594984807715031</v>
+        <v>0.537118541540643</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1380551814850656</v>
+        <v>0.1396051814850656</v>
       </c>
       <c r="C27">
-        <v>1.996404558438802</v>
+        <v>1.926293082010684</v>
       </c>
       <c r="D27">
-        <v>2.951404558438802</v>
+        <v>2.919493082010684</v>
       </c>
       <c r="E27">
-        <v>0.795</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="F27">
-        <v>0.9550000000000001</v>
+        <v>0.9932000000000001</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3489,37 +3489,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M27">
-        <v>0.191764</v>
+        <v>0.19943456</v>
       </c>
       <c r="N27">
-        <v>-0.08876400000000015</v>
+        <v>-0.09643456000000014</v>
       </c>
       <c r="O27">
-        <v>-0.01686516000000003</v>
+        <v>-0.01832256640000003</v>
       </c>
       <c r="P27">
-        <v>-0.07189884000000012</v>
+        <v>-0.07811199360000011</v>
       </c>
       <c r="Q27">
-        <v>0.5971011599999999</v>
+        <v>0.5908880063999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1239709575123737</v>
+        <v>0.1250273218030814</v>
       </c>
       <c r="T27">
-        <v>1.431728539345475</v>
+        <v>1.451076222309603</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1020525228927222</v>
+        <v>0.0981274258583867</v>
       </c>
       <c r="W27">
-        <v>0.1803078534031414</v>
+        <v>0.1810960128876359</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.537118541540643</v>
+        <v>0.5164601360967721</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1396051814850656</v>
+        <v>0.1508330155723226</v>
       </c>
       <c r="C28">
-        <v>1.926293082010684</v>
+        <v>1.676041496753494</v>
       </c>
       <c r="D28">
-        <v>2.919493082010684</v>
+        <v>2.707441496753494</v>
       </c>
       <c r="E28">
-        <v>0.8332000000000001</v>
+        <v>0.8714000000000001</v>
       </c>
       <c r="F28">
-        <v>0.9932000000000001</v>
+        <v>1.0314</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3571,45 +3571,45 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M28">
-        <v>0.19943456</v>
+        <v>0.24320412</v>
       </c>
       <c r="N28">
-        <v>-0.09643456000000014</v>
+        <v>-0.1402041200000002</v>
       </c>
       <c r="O28">
-        <v>-0.01832256640000003</v>
+        <v>-0.02663878280000003</v>
       </c>
       <c r="P28">
-        <v>-0.07811199360000011</v>
+        <v>-0.1135653372000001</v>
       </c>
       <c r="Q28">
-        <v>0.5908880063999999</v>
+        <v>0.5554346628</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1250273218030814</v>
+        <v>0.126424729070599</v>
       </c>
       <c r="T28">
-        <v>1.451076222309603</v>
+        <v>1.476670227163349</v>
       </c>
       <c r="U28">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.0981274258583867</v>
+        <v>0.08046738681894029</v>
       </c>
       <c r="W28">
-        <v>0.1810960128876359</v>
+        <v>0.2168257901880939</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5164601360967721</v>
+        <v>0.4235125622049489</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1508330155723226</v>
+        <v>0.1527330155723226</v>
       </c>
       <c r="C29">
-        <v>1.676041496753494</v>
+        <v>1.604968042679929</v>
       </c>
       <c r="D29">
-        <v>2.707441496753494</v>
+        <v>2.674568042679929</v>
       </c>
       <c r="E29">
-        <v>0.8714000000000001</v>
+        <v>0.9096000000000001</v>
       </c>
       <c r="F29">
-        <v>1.0314</v>
+        <v>1.0696</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3653,37 +3653,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M29">
-        <v>0.24320412</v>
+        <v>0.25221168</v>
       </c>
       <c r="N29">
-        <v>-0.1402041200000002</v>
+        <v>-0.1492116800000002</v>
       </c>
       <c r="O29">
-        <v>-0.02663878280000003</v>
+        <v>-0.02835021920000003</v>
       </c>
       <c r="P29">
-        <v>-0.1135653372000001</v>
+        <v>-0.1208614608000002</v>
       </c>
       <c r="Q29">
-        <v>0.5554346628</v>
+        <v>0.5481385391999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.126424729070599</v>
+        <v>0.1275445169743573</v>
       </c>
       <c r="T29">
-        <v>1.476670227163349</v>
+        <v>1.497179535873951</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.08046738681894029</v>
+        <v>0.07759355157540671</v>
       </c>
       <c r="W29">
-        <v>0.2168257901880939</v>
+        <v>0.2175034405385191</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4235125622049489</v>
+        <v>0.4083871135547721</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1527330155723226</v>
+        <v>0.1546330155723226</v>
       </c>
       <c r="C30">
-        <v>1.604968042679929</v>
+        <v>1.534683303773867</v>
       </c>
       <c r="D30">
-        <v>2.674568042679929</v>
+        <v>2.642483303773867</v>
       </c>
       <c r="E30">
-        <v>0.9096000000000001</v>
+        <v>0.9478000000000001</v>
       </c>
       <c r="F30">
-        <v>1.0696</v>
+        <v>1.1078</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3735,37 +3735,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M30">
-        <v>0.25221168</v>
+        <v>0.26121924</v>
       </c>
       <c r="N30">
-        <v>-0.1492116800000002</v>
+        <v>-0.1582192400000001</v>
       </c>
       <c r="O30">
-        <v>-0.02835021920000003</v>
+        <v>-0.03006165560000003</v>
       </c>
       <c r="P30">
-        <v>-0.1208614608000002</v>
+        <v>-0.1281575844000001</v>
       </c>
       <c r="Q30">
-        <v>0.5481385391999999</v>
+        <v>0.5408424155999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1275445169743573</v>
+        <v>0.1286958481993483</v>
       </c>
       <c r="T30">
-        <v>1.497179535873951</v>
+        <v>1.518266571590485</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.07759355157540671</v>
+        <v>0.07491791186590993</v>
       </c>
       <c r="W30">
-        <v>0.2175034405385191</v>
+        <v>0.2181343563820184</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4083871135547721</v>
+        <v>0.3943047992942628</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1546330155723226</v>
+        <v>0.1565330155723226</v>
       </c>
       <c r="C31">
-        <v>1.534683303773867</v>
+        <v>1.465159231679354</v>
       </c>
       <c r="D31">
-        <v>2.642483303773867</v>
+        <v>2.611159231679354</v>
       </c>
       <c r="E31">
-        <v>0.9477999999999999</v>
+        <v>0.9860000000000001</v>
       </c>
       <c r="F31">
-        <v>1.1078</v>
+        <v>1.146</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3817,37 +3817,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M31">
-        <v>0.26121924</v>
+        <v>0.2702268</v>
       </c>
       <c r="N31">
-        <v>-0.1582192400000001</v>
+        <v>-0.1672268000000002</v>
       </c>
       <c r="O31">
-        <v>-0.03006165560000002</v>
+        <v>-0.03177309200000003</v>
       </c>
       <c r="P31">
-        <v>-0.1281575844000001</v>
+        <v>-0.1354537080000001</v>
       </c>
       <c r="Q31">
-        <v>0.5408424156</v>
+        <v>0.5335462919999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1286958481993483</v>
+        <v>0.1298800746021961</v>
       </c>
       <c r="T31">
-        <v>1.518266571590485</v>
+        <v>1.539956094041778</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.07491791186590994</v>
+        <v>0.07242064813704625</v>
       </c>
       <c r="W31">
-        <v>0.2181343563820184</v>
+        <v>0.2187232111692845</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3943047992942629</v>
+        <v>0.381161305984454</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1565330155723226</v>
+        <v>0.1584330155723226</v>
       </c>
       <c r="C32">
-        <v>1.465159231679354</v>
+        <v>1.396369092403966</v>
       </c>
       <c r="D32">
-        <v>2.611159231679354</v>
+        <v>2.580569092403966</v>
       </c>
       <c r="E32">
-        <v>0.9860000000000001</v>
+        <v>1.0242</v>
       </c>
       <c r="F32">
-        <v>1.146</v>
+        <v>1.1842</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3899,37 +3899,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M32">
-        <v>0.2702268</v>
+        <v>0.2792343600000001</v>
       </c>
       <c r="N32">
-        <v>-0.1672268000000002</v>
+        <v>-0.1762343600000002</v>
       </c>
       <c r="O32">
-        <v>-0.03177309200000003</v>
+        <v>-0.03348452840000004</v>
       </c>
       <c r="P32">
-        <v>-0.1354537080000001</v>
+        <v>-0.1427498316000002</v>
       </c>
       <c r="Q32">
-        <v>0.5335462919999999</v>
+        <v>0.5262501683999998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1298800746021961</v>
+        <v>0.131098626408025</v>
       </c>
       <c r="T32">
-        <v>1.539956094041778</v>
+        <v>1.562274298303253</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.07242064813704625</v>
+        <v>0.07008449819714153</v>
       </c>
       <c r="W32">
-        <v>0.2187232111692845</v>
+        <v>0.219274075325114</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.381161305984454</v>
+        <v>0.3688657799849554</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1584330155723226</v>
+        <v>0.1603330155723226</v>
       </c>
       <c r="C33">
-        <v>1.396369092403966</v>
+        <v>1.328287390220434</v>
       </c>
       <c r="D33">
-        <v>2.580569092403966</v>
+        <v>2.550687390220434</v>
       </c>
       <c r="E33">
-        <v>1.0242</v>
+        <v>1.0624</v>
       </c>
       <c r="F33">
-        <v>1.1842</v>
+        <v>1.2224</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3981,37 +3981,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M33">
-        <v>0.2792343600000001</v>
+        <v>0.28824192</v>
       </c>
       <c r="N33">
-        <v>-0.1762343600000002</v>
+        <v>-0.1852419200000002</v>
       </c>
       <c r="O33">
-        <v>-0.03348452840000004</v>
+        <v>-0.03519596480000003</v>
       </c>
       <c r="P33">
-        <v>-0.1427498316000002</v>
+        <v>-0.1500459552000001</v>
       </c>
       <c r="Q33">
-        <v>0.5262501683999998</v>
+        <v>0.5189540447999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.131098626408025</v>
+        <v>0.1323530179728489</v>
       </c>
       <c r="T33">
-        <v>1.562274298303253</v>
+        <v>1.585248920337125</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.07008449819714153</v>
+        <v>0.06789435762848087</v>
       </c>
       <c r="W33">
-        <v>0.219274075325114</v>
+        <v>0.2197905104712042</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3688657799849554</v>
+        <v>0.3573387243604256</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1603330155723226</v>
+        <v>0.1622330155723226</v>
       </c>
       <c r="C34">
-        <v>1.328287390220434</v>
+        <v>1.260889796794851</v>
       </c>
       <c r="D34">
-        <v>2.550687390220434</v>
+        <v>2.521489796794851</v>
       </c>
       <c r="E34">
-        <v>1.0624</v>
+        <v>1.1006</v>
       </c>
       <c r="F34">
-        <v>1.2224</v>
+        <v>1.2606</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4063,37 +4063,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M34">
-        <v>0.28824192</v>
+        <v>0.2972494800000001</v>
       </c>
       <c r="N34">
-        <v>-0.1852419200000002</v>
+        <v>-0.1942494800000002</v>
       </c>
       <c r="O34">
-        <v>-0.03519596480000003</v>
+        <v>-0.03690740120000004</v>
       </c>
       <c r="P34">
-        <v>-0.1500459552000001</v>
+        <v>-0.1573420788000002</v>
       </c>
       <c r="Q34">
-        <v>0.5189540447999998</v>
+        <v>0.5116579211999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1323530179728489</v>
+        <v>0.1336448540619959</v>
       </c>
       <c r="T34">
-        <v>1.585248920337125</v>
+        <v>1.608909351983947</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06789435762848087</v>
+        <v>0.06583695285186023</v>
       </c>
       <c r="W34">
-        <v>0.2197905104712042</v>
+        <v>0.2202756465175314</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3573387243604256</v>
+        <v>0.3465102781676854</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1622330155723226</v>
+        <v>0.1641330155723226</v>
       </c>
       <c r="C35">
-        <v>1.260889796794851</v>
+        <v>1.194153085127369</v>
       </c>
       <c r="D35">
-        <v>2.521489796794851</v>
+        <v>2.492953085127369</v>
       </c>
       <c r="E35">
-        <v>1.1006</v>
+        <v>1.1388</v>
       </c>
       <c r="F35">
-        <v>1.2606</v>
+        <v>1.2988</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4145,37 +4145,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M35">
-        <v>0.2972494800000001</v>
+        <v>0.30625704</v>
       </c>
       <c r="N35">
-        <v>-0.1942494800000002</v>
+        <v>-0.2032570400000002</v>
       </c>
       <c r="O35">
-        <v>-0.03690740120000004</v>
+        <v>-0.03861883760000003</v>
       </c>
       <c r="P35">
-        <v>-0.1573420788000002</v>
+        <v>-0.1646382024000001</v>
       </c>
       <c r="Q35">
-        <v>0.5116579211999999</v>
+        <v>0.5043617975999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1336448540619959</v>
+        <v>0.1349758366992989</v>
       </c>
       <c r="T35">
-        <v>1.608909351983947</v>
+        <v>1.633286766407946</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06583695285186023</v>
+        <v>0.06390057188562906</v>
       </c>
       <c r="W35">
-        <v>0.2202756465175314</v>
+        <v>0.2207322451493687</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3465102781676854</v>
+        <v>0.3363187993980477</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1641330155723226</v>
+        <v>0.1660330155723226</v>
       </c>
       <c r="C36">
-        <v>1.194153085127369</v>
+        <v>1.128055067928428</v>
       </c>
       <c r="D36">
-        <v>2.492953085127369</v>
+        <v>2.465055067928428</v>
       </c>
       <c r="E36">
-        <v>1.1388</v>
+        <v>1.177</v>
       </c>
       <c r="F36">
-        <v>1.2988</v>
+        <v>1.337</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4227,37 +4227,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M36">
-        <v>0.30625704</v>
+        <v>0.3152646000000001</v>
       </c>
       <c r="N36">
-        <v>-0.2032570400000002</v>
+        <v>-0.2122646000000002</v>
       </c>
       <c r="O36">
-        <v>-0.03861883760000003</v>
+        <v>-0.04033027400000003</v>
       </c>
       <c r="P36">
-        <v>-0.1646382024000001</v>
+        <v>-0.1719343260000002</v>
       </c>
       <c r="Q36">
-        <v>0.5043617975999999</v>
+        <v>0.4970656739999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1349758366992989</v>
+        <v>0.1363477726485189</v>
       </c>
       <c r="T36">
-        <v>1.633286766407946</v>
+        <v>1.658414255121915</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.06390057188562906</v>
+        <v>0.06207484126032536</v>
       </c>
       <c r="W36">
-        <v>0.2207322451493687</v>
+        <v>0.2211627524308153</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3363187993980477</v>
+        <v>0.3267096908438177</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1660330155723226</v>
+        <v>0.1679330155723227</v>
       </c>
       <c r="C37">
-        <v>1.128055067928428</v>
+        <v>1.062574540086881</v>
       </c>
       <c r="D37">
-        <v>2.465055067928428</v>
+        <v>2.437774540086882</v>
       </c>
       <c r="E37">
-        <v>1.177</v>
+        <v>1.2152</v>
       </c>
       <c r="F37">
-        <v>1.337</v>
+        <v>1.3752</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4309,37 +4309,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M37">
-        <v>0.3152646000000001</v>
+        <v>0.3242721600000001</v>
       </c>
       <c r="N37">
-        <v>-0.2122646000000002</v>
+        <v>-0.2212721600000002</v>
       </c>
       <c r="O37">
-        <v>-0.04033027400000003</v>
+        <v>-0.04204171040000004</v>
       </c>
       <c r="P37">
-        <v>-0.1719343260000002</v>
+        <v>-0.1792304496000002</v>
       </c>
       <c r="Q37">
-        <v>0.4970656739999999</v>
+        <v>0.4897695503999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1363477726485189</v>
+        <v>0.137762581596152</v>
       </c>
       <c r="T37">
-        <v>1.658414255121915</v>
+        <v>1.684326977858195</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.06207484126032536</v>
+        <v>0.06035054011420522</v>
       </c>
       <c r="W37">
-        <v>0.2211627524308153</v>
+        <v>0.2215693426410704</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3267096908438177</v>
+        <v>0.3176344216537116</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1679330155723226</v>
+        <v>0.1698330155723226</v>
       </c>
       <c r="C38">
-        <v>1.062574540086882</v>
+        <v>0.9976912249165155</v>
       </c>
       <c r="D38">
-        <v>2.437774540086882</v>
+        <v>2.411091224916516</v>
       </c>
       <c r="E38">
-        <v>1.2152</v>
+        <v>1.2534</v>
       </c>
       <c r="F38">
-        <v>1.3752</v>
+        <v>1.4134</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4391,37 +4391,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M38">
-        <v>0.32427216</v>
+        <v>0.33327972</v>
       </c>
       <c r="N38">
-        <v>-0.2212721600000002</v>
+        <v>-0.2302797200000001</v>
       </c>
       <c r="O38">
-        <v>-0.04204171040000003</v>
+        <v>-0.04375314680000002</v>
       </c>
       <c r="P38">
-        <v>-0.1792304496000001</v>
+        <v>-0.1865265732000001</v>
       </c>
       <c r="Q38">
-        <v>0.4897695503999999</v>
+        <v>0.4824734267999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.137762581596152</v>
+        <v>0.1392223051135512</v>
       </c>
       <c r="T38">
-        <v>1.684326977858195</v>
+        <v>1.711062326713087</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.06035054011420522</v>
+        <v>0.05871944443544292</v>
       </c>
       <c r="W38">
-        <v>0.2215693426410704</v>
+        <v>0.2219539550021226</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3176344216537117</v>
+        <v>0.3090497075549627</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1698330155723226</v>
+        <v>0.1717330155723226</v>
       </c>
       <c r="C39">
-        <v>0.9976912249165155</v>
+        <v>0.9333857238945737</v>
       </c>
       <c r="D39">
-        <v>2.411091224916516</v>
+        <v>2.384985723894574</v>
       </c>
       <c r="E39">
-        <v>1.2534</v>
+        <v>1.2916</v>
       </c>
       <c r="F39">
-        <v>1.4134</v>
+        <v>1.4516</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4473,37 +4473,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M39">
-        <v>0.33327972</v>
+        <v>0.3422872800000001</v>
       </c>
       <c r="N39">
-        <v>-0.2302797200000001</v>
+        <v>-0.2392872800000002</v>
       </c>
       <c r="O39">
-        <v>-0.04375314680000002</v>
+        <v>-0.04546458320000004</v>
       </c>
       <c r="P39">
-        <v>-0.1865265732000001</v>
+        <v>-0.1938226968000002</v>
       </c>
       <c r="Q39">
-        <v>0.4824734267999999</v>
+        <v>0.4751773031999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1392223051135512</v>
+        <v>0.1407291164863504</v>
       </c>
       <c r="T39">
-        <v>1.711062326713087</v>
+        <v>1.738660106176201</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05871944443544292</v>
+        <v>0.0571741958976681</v>
       </c>
       <c r="W39">
-        <v>0.2219539550021226</v>
+        <v>0.2223183246073299</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3090497075549627</v>
+        <v>0.3009168205140426</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1717330155723226</v>
+        <v>0.1736330155723226</v>
       </c>
       <c r="C40">
-        <v>0.9333857238945737</v>
+        <v>0.869639469630477</v>
       </c>
       <c r="D40">
-        <v>2.384985723894574</v>
+        <v>2.359439469630477</v>
       </c>
       <c r="E40">
-        <v>1.2916</v>
+        <v>1.3298</v>
       </c>
       <c r="F40">
-        <v>1.4516</v>
+        <v>1.4898</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4555,37 +4555,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M40">
-        <v>0.3422872800000001</v>
+        <v>0.3512948400000001</v>
       </c>
       <c r="N40">
-        <v>-0.2392872800000002</v>
+        <v>-0.2482948400000002</v>
       </c>
       <c r="O40">
-        <v>-0.04546458320000004</v>
+        <v>-0.04717601960000004</v>
       </c>
       <c r="P40">
-        <v>-0.1938226968000002</v>
+        <v>-0.2011188204000001</v>
       </c>
       <c r="Q40">
-        <v>0.4751773031999998</v>
+        <v>0.4678811795999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1407291164863504</v>
+        <v>0.1422853315107168</v>
       </c>
       <c r="T40">
-        <v>1.738660106176201</v>
+        <v>1.767162730867614</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.0571741958976681</v>
+        <v>0.05570819087465097</v>
       </c>
       <c r="W40">
-        <v>0.2223183246073299</v>
+        <v>0.2226640085917573</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3009168205140426</v>
+        <v>0.2932010046034261</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1736330155723226</v>
+        <v>0.1755330155723226</v>
       </c>
       <c r="C41">
-        <v>0.869639469630477</v>
+        <v>0.8064346818251031</v>
       </c>
       <c r="D41">
-        <v>2.359439469630477</v>
+        <v>2.334434681825103</v>
       </c>
       <c r="E41">
-        <v>1.3298</v>
+        <v>1.368</v>
       </c>
       <c r="F41">
-        <v>1.4898</v>
+        <v>1.528</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4637,37 +4637,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M41">
-        <v>0.3512948400000001</v>
+        <v>0.3603024000000001</v>
       </c>
       <c r="N41">
-        <v>-0.2482948400000002</v>
+        <v>-0.2573024000000002</v>
       </c>
       <c r="O41">
-        <v>-0.04717601960000004</v>
+        <v>-0.04888745600000004</v>
       </c>
       <c r="P41">
-        <v>-0.2011188204000001</v>
+        <v>-0.2084149440000002</v>
       </c>
       <c r="Q41">
-        <v>0.4678811795999999</v>
+        <v>0.4605850559999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1422853315107168</v>
+        <v>0.1438934203692288</v>
       </c>
       <c r="T41">
-        <v>1.767162730867614</v>
+        <v>1.796615443048741</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05570819087465097</v>
+        <v>0.05431548610278469</v>
       </c>
       <c r="W41">
-        <v>0.2226640085917573</v>
+        <v>0.2229924083769634</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2932010046034261</v>
+        <v>0.2858709794883405</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1755330155723226</v>
+        <v>0.1774330155723226</v>
       </c>
       <c r="C42">
-        <v>0.8064346818251031</v>
+        <v>0.7437543260010955</v>
       </c>
       <c r="D42">
-        <v>2.334434681825103</v>
+        <v>2.309954326001096</v>
       </c>
       <c r="E42">
-        <v>1.368</v>
+        <v>1.4062</v>
       </c>
       <c r="F42">
-        <v>1.528</v>
+        <v>1.5662</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4719,37 +4719,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M42">
-        <v>0.3603024000000001</v>
+        <v>0.3693099600000001</v>
       </c>
       <c r="N42">
-        <v>-0.2573024000000002</v>
+        <v>-0.2663099600000002</v>
       </c>
       <c r="O42">
-        <v>-0.04888745600000004</v>
+        <v>-0.05059889240000005</v>
       </c>
       <c r="P42">
-        <v>-0.2084149440000002</v>
+        <v>-0.2157110676000002</v>
       </c>
       <c r="Q42">
-        <v>0.4605850559999999</v>
+        <v>0.4532889323999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1438934203692288</v>
+        <v>0.14555602071447</v>
       </c>
       <c r="T42">
-        <v>1.796615443048741</v>
+        <v>1.827066552252957</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05431548610278469</v>
+        <v>0.05299071814905823</v>
       </c>
       <c r="W42">
-        <v>0.2229924083769634</v>
+        <v>0.2233047886604521</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2858709794883405</v>
+        <v>0.2788985165739907</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1774330155723226</v>
+        <v>0.1793330155723226</v>
       </c>
       <c r="C43">
-        <v>0.7437543260010955</v>
+        <v>0.6815820748029056</v>
       </c>
       <c r="D43">
-        <v>2.309954326001096</v>
+        <v>2.285982074802906</v>
       </c>
       <c r="E43">
-        <v>1.4062</v>
+        <v>1.4444</v>
       </c>
       <c r="F43">
-        <v>1.5662</v>
+        <v>1.6044</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4801,37 +4801,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M43">
-        <v>0.3693099600000001</v>
+        <v>0.3783175200000001</v>
       </c>
       <c r="N43">
-        <v>-0.2663099600000002</v>
+        <v>-0.2753175200000002</v>
       </c>
       <c r="O43">
-        <v>-0.05059889240000005</v>
+        <v>-0.05231032880000004</v>
       </c>
       <c r="P43">
-        <v>-0.2157110676000002</v>
+        <v>-0.2230071912000002</v>
       </c>
       <c r="Q43">
-        <v>0.4532889323999998</v>
+        <v>0.4459928087999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.14555602071447</v>
+        <v>0.1472759521060988</v>
       </c>
       <c r="T43">
-        <v>1.827066552252957</v>
+        <v>1.858567699705594</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05299071814905823</v>
+        <v>0.05172903438360447</v>
       </c>
       <c r="W43">
-        <v>0.2233047886604521</v>
+        <v>0.2236022936923461</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2788985165739907</v>
+        <v>0.2722580757031814</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1793330155723226</v>
+        <v>0.1812330155723226</v>
       </c>
       <c r="C44">
-        <v>0.6815820748029058</v>
+        <v>0.6199022716818086</v>
       </c>
       <c r="D44">
-        <v>2.285982074802906</v>
+        <v>2.262502271681809</v>
       </c>
       <c r="E44">
-        <v>1.4444</v>
+        <v>1.4826</v>
       </c>
       <c r="F44">
-        <v>1.6044</v>
+        <v>1.6426</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4883,37 +4883,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M44">
-        <v>0.37831752</v>
+        <v>0.38732508</v>
       </c>
       <c r="N44">
-        <v>-0.2753175200000001</v>
+        <v>-0.2843250800000002</v>
       </c>
       <c r="O44">
-        <v>-0.05231032880000003</v>
+        <v>-0.05402176520000004</v>
       </c>
       <c r="P44">
-        <v>-0.2230071912000001</v>
+        <v>-0.2303033148000001</v>
       </c>
       <c r="Q44">
-        <v>0.4459928087999999</v>
+        <v>0.4386966851999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1472759521060987</v>
+        <v>0.1490562319676092</v>
       </c>
       <c r="T44">
-        <v>1.858567699705594</v>
+        <v>1.891174150577622</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05172903438360447</v>
+        <v>0.05052603358398577</v>
       </c>
       <c r="W44">
-        <v>0.2236022936923461</v>
+        <v>0.2238859612808962</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2722580757031815</v>
+        <v>0.2659264925472935</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1812330155723226</v>
+        <v>0.1831330155723226</v>
       </c>
       <c r="C45">
-        <v>0.6199022716818086</v>
+        <v>0.5586998967961589</v>
       </c>
       <c r="D45">
-        <v>2.262502271681809</v>
+        <v>2.239499896796159</v>
       </c>
       <c r="E45">
-        <v>1.4826</v>
+        <v>1.5208</v>
       </c>
       <c r="F45">
-        <v>1.6426</v>
+        <v>1.6808</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4965,37 +4965,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M45">
-        <v>0.38732508</v>
+        <v>0.39633264</v>
       </c>
       <c r="N45">
-        <v>-0.2843250800000002</v>
+        <v>-0.2933326400000001</v>
       </c>
       <c r="O45">
-        <v>-0.05402176520000004</v>
+        <v>-0.05573320160000002</v>
       </c>
       <c r="P45">
-        <v>-0.2303033148000001</v>
+        <v>-0.2375994384000001</v>
       </c>
       <c r="Q45">
-        <v>0.4386966851999999</v>
+        <v>0.4314005616</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1490562319676092</v>
+        <v>0.1509000932527451</v>
       </c>
       <c r="T45">
-        <v>1.891174150577622</v>
+        <v>1.924945117552223</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05052603358398577</v>
+        <v>0.04937771463889518</v>
       </c>
       <c r="W45">
-        <v>0.2238859612808962</v>
+        <v>0.2241567348881485</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2659264925472935</v>
+        <v>0.2598827086257641</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1831330155723226</v>
+        <v>0.1850330155723227</v>
       </c>
       <c r="C46">
-        <v>0.5586998967961589</v>
+        <v>0.4979605349708194</v>
       </c>
       <c r="D46">
-        <v>2.239499896796159</v>
+        <v>2.216960534970819</v>
       </c>
       <c r="E46">
-        <v>1.5208</v>
+        <v>1.559</v>
       </c>
       <c r="F46">
-        <v>1.6808</v>
+        <v>1.719</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5047,37 +5047,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M46">
-        <v>0.39633264</v>
+        <v>0.4053402</v>
       </c>
       <c r="N46">
-        <v>-0.2933326400000001</v>
+        <v>-0.3023402000000002</v>
       </c>
       <c r="O46">
-        <v>-0.05573320160000002</v>
+        <v>-0.05744463800000003</v>
       </c>
       <c r="P46">
-        <v>-0.2375994384000001</v>
+        <v>-0.2448955620000001</v>
       </c>
       <c r="Q46">
-        <v>0.4314005616</v>
+        <v>0.4241044379999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1509000932527451</v>
+        <v>0.1528110040391587</v>
       </c>
       <c r="T46">
-        <v>1.924945117552223</v>
+        <v>1.959944119689536</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04937771463889518</v>
+        <v>0.04828043209136418</v>
       </c>
       <c r="W46">
-        <v>0.2241567348881485</v>
+        <v>0.2244154741128563</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2598827086257641</v>
+        <v>0.2541075373229693</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1850330155723227</v>
+        <v>0.1869330155723226</v>
       </c>
       <c r="C47">
-        <v>0.4979605349708194</v>
+        <v>0.4376703455721367</v>
       </c>
       <c r="D47">
-        <v>2.216960534970819</v>
+        <v>2.194870345572137</v>
       </c>
       <c r="E47">
-        <v>1.559</v>
+        <v>1.5972</v>
       </c>
       <c r="F47">
-        <v>1.719</v>
+        <v>1.7572</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5129,37 +5129,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M47">
-        <v>0.4053402</v>
+        <v>0.4143477600000001</v>
       </c>
       <c r="N47">
-        <v>-0.3023402000000002</v>
+        <v>-0.3113477600000002</v>
       </c>
       <c r="O47">
-        <v>-0.05744463800000003</v>
+        <v>-0.05915607440000004</v>
       </c>
       <c r="P47">
-        <v>-0.2448955620000001</v>
+        <v>-0.2521916856000002</v>
       </c>
       <c r="Q47">
-        <v>0.4241044379999999</v>
+        <v>0.4168083143999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1528110040391587</v>
+        <v>0.1547926892991431</v>
       </c>
       <c r="T47">
-        <v>1.959944119689536</v>
+        <v>1.996239381165268</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04828043209136418</v>
+        <v>0.04723085748068234</v>
       </c>
       <c r="W47">
-        <v>0.2244154741128563</v>
+        <v>0.2246629638060551</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2541075373229693</v>
+        <v>0.248583460424644</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1869330155723226</v>
+        <v>0.1888330155723226</v>
       </c>
       <c r="C48">
-        <v>0.4376703455721367</v>
+        <v>0.3778160341661749</v>
       </c>
       <c r="D48">
-        <v>2.194870345572137</v>
+        <v>2.173216034166175</v>
       </c>
       <c r="E48">
-        <v>1.5972</v>
+        <v>1.6354</v>
       </c>
       <c r="F48">
-        <v>1.7572</v>
+        <v>1.7954</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5211,37 +5211,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M48">
-        <v>0.4143477600000001</v>
+        <v>0.4233553200000001</v>
       </c>
       <c r="N48">
-        <v>-0.3113477600000002</v>
+        <v>-0.3203553200000002</v>
       </c>
       <c r="O48">
-        <v>-0.05915607440000004</v>
+        <v>-0.06086751080000005</v>
       </c>
       <c r="P48">
-        <v>-0.2521916856000002</v>
+        <v>-0.2594878092000002</v>
       </c>
       <c r="Q48">
-        <v>0.4168083143999999</v>
+        <v>0.4095121907999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1547926892991431</v>
+        <v>0.156849155134976</v>
       </c>
       <c r="T48">
-        <v>1.996239381165268</v>
+        <v>2.033904275149518</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04723085748068234</v>
+        <v>0.04622594561939123</v>
       </c>
       <c r="W48">
-        <v>0.2246629638060551</v>
+        <v>0.2248999220229476</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.248583460424644</v>
+        <v>0.2432944506283748</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1888330155723226</v>
+        <v>0.1907330155723226</v>
       </c>
       <c r="C49">
-        <v>0.3778160341661749</v>
+        <v>0.3183848258382593</v>
       </c>
       <c r="D49">
-        <v>2.173216034166175</v>
+        <v>2.15198482583826</v>
       </c>
       <c r="E49">
-        <v>1.6354</v>
+        <v>1.6736</v>
       </c>
       <c r="F49">
-        <v>1.7954</v>
+        <v>1.8336</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5293,37 +5293,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M49">
-        <v>0.4233553200000001</v>
+        <v>0.4323628800000001</v>
       </c>
       <c r="N49">
-        <v>-0.3203553200000002</v>
+        <v>-0.3293628800000002</v>
       </c>
       <c r="O49">
-        <v>-0.06086751080000005</v>
+        <v>-0.06257894720000005</v>
       </c>
       <c r="P49">
-        <v>-0.2594878092000002</v>
+        <v>-0.2667839328000002</v>
       </c>
       <c r="Q49">
-        <v>0.4095121907999998</v>
+        <v>0.4022160671999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.156849155134976</v>
+        <v>0.1589847158106486</v>
       </c>
       <c r="T49">
-        <v>2.033904275149518</v>
+        <v>2.073017818902394</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04622594561939123</v>
+        <v>0.04526290508565391</v>
       </c>
       <c r="W49">
-        <v>0.2248999220229476</v>
+        <v>0.2251270069808028</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2432944506283748</v>
+        <v>0.2382258162402837</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1907330155723226</v>
+        <v>0.1926330155723227</v>
       </c>
       <c r="C50">
-        <v>0.3183848258382596</v>
+        <v>0.2593644400613118</v>
       </c>
       <c r="D50">
-        <v>2.15198482583826</v>
+        <v>2.131164440061312</v>
       </c>
       <c r="E50">
-        <v>1.6736</v>
+        <v>1.7118</v>
       </c>
       <c r="F50">
-        <v>1.8336</v>
+        <v>1.8718</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5375,37 +5375,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M50">
-        <v>0.4323628800000001</v>
+        <v>0.44137044</v>
       </c>
       <c r="N50">
-        <v>-0.3293628800000002</v>
+        <v>-0.3383704400000002</v>
       </c>
       <c r="O50">
-        <v>-0.06257894720000004</v>
+        <v>-0.06429038360000003</v>
       </c>
       <c r="P50">
-        <v>-0.2667839328000001</v>
+        <v>-0.2740800564000001</v>
       </c>
       <c r="Q50">
-        <v>0.4022160671999999</v>
+        <v>0.3949199435999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1589847158106486</v>
+        <v>0.1612040239637986</v>
       </c>
       <c r="T50">
-        <v>2.073017818902393</v>
+        <v>2.113665227116166</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04526290508565391</v>
+        <v>0.04433917232880383</v>
       </c>
       <c r="W50">
-        <v>0.2251270069808028</v>
+        <v>0.2253448231648681</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2382258162402837</v>
+        <v>0.2333640648884412</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1926330155723227</v>
+        <v>0.1945330155723226</v>
       </c>
       <c r="C51">
-        <v>0.2593644400613118</v>
+        <v>0.2007430670090988</v>
       </c>
       <c r="D51">
-        <v>2.131164440061312</v>
+        <v>2.110743067009099</v>
       </c>
       <c r="E51">
-        <v>1.7118</v>
+        <v>1.75</v>
       </c>
       <c r="F51">
-        <v>1.8718</v>
+        <v>1.91</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5457,37 +5457,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M51">
-        <v>0.44137044</v>
+        <v>0.4503780000000001</v>
       </c>
       <c r="N51">
-        <v>-0.3383704400000002</v>
+        <v>-0.3473780000000002</v>
       </c>
       <c r="O51">
-        <v>-0.06429038360000003</v>
+        <v>-0.06600182000000003</v>
       </c>
       <c r="P51">
-        <v>-0.2740800564000001</v>
+        <v>-0.2813761800000001</v>
       </c>
       <c r="Q51">
-        <v>0.3949199435999999</v>
+        <v>0.3876238199999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1612040239637986</v>
+        <v>0.1635121044430745</v>
       </c>
       <c r="T51">
-        <v>2.113665227116166</v>
+        <v>2.155938531658489</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04433917232880383</v>
+        <v>0.04345238888222776</v>
       </c>
       <c r="W51">
-        <v>0.2253448231648681</v>
+        <v>0.2255539267015707</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2333640648884412</v>
+        <v>0.2286967835906724</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1945330155723226</v>
+        <v>0.1964330155723226</v>
       </c>
       <c r="C52">
-        <v>0.2007430670090988</v>
+        <v>0.1425093452183834</v>
       </c>
       <c r="D52">
-        <v>2.110743067009099</v>
+        <v>2.090709345218384</v>
       </c>
       <c r="E52">
-        <v>1.75</v>
+        <v>1.7882</v>
       </c>
       <c r="F52">
-        <v>1.91</v>
+        <v>1.9482</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5539,37 +5539,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M52">
-        <v>0.4503780000000001</v>
+        <v>0.4593855600000001</v>
       </c>
       <c r="N52">
-        <v>-0.3473780000000002</v>
+        <v>-0.3563855600000002</v>
       </c>
       <c r="O52">
-        <v>-0.06600182000000003</v>
+        <v>-0.06771325640000005</v>
       </c>
       <c r="P52">
-        <v>-0.2813761800000001</v>
+        <v>-0.2886723036000002</v>
       </c>
       <c r="Q52">
-        <v>0.3876238199999999</v>
+        <v>0.3803276963999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1635121044430745</v>
+        <v>0.1659143922888516</v>
       </c>
       <c r="T52">
-        <v>2.155938531658489</v>
+        <v>2.19993727720254</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04345238888222776</v>
+        <v>0.04260038125708603</v>
       </c>
       <c r="W52">
-        <v>0.2255539267015707</v>
+        <v>0.2257548300995791</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2286967835906724</v>
+        <v>0.2242125329320318</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1964330155723226</v>
+        <v>0.1983330155723226</v>
       </c>
       <c r="C53">
-        <v>0.1425093452183834</v>
+        <v>0.08465234051121939</v>
       </c>
       <c r="D53">
-        <v>2.090709345218384</v>
+        <v>2.07105234051122</v>
       </c>
       <c r="E53">
-        <v>1.7882</v>
+        <v>1.8264</v>
       </c>
       <c r="F53">
-        <v>1.9482</v>
+        <v>1.9864</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5621,37 +5621,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M53">
-        <v>0.4593855600000001</v>
+        <v>0.4683931200000001</v>
       </c>
       <c r="N53">
-        <v>-0.3563855600000002</v>
+        <v>-0.3653931200000002</v>
       </c>
       <c r="O53">
-        <v>-0.06771325640000005</v>
+        <v>-0.06942469280000003</v>
       </c>
       <c r="P53">
-        <v>-0.2886723036000002</v>
+        <v>-0.2959684272000002</v>
       </c>
       <c r="Q53">
-        <v>0.3803276963999999</v>
+        <v>0.3730315727999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1659143922888516</v>
+        <v>0.168416775461536</v>
       </c>
       <c r="T53">
-        <v>2.19993727720254</v>
+        <v>2.245769303810926</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04260038125708603</v>
+        <v>0.04178114315598823</v>
       </c>
       <c r="W53">
-        <v>0.2257548300995791</v>
+        <v>0.225948006443818</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2242125329320318</v>
+        <v>0.2199007534525697</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1983330155723226</v>
+        <v>0.2002330155723226</v>
       </c>
       <c r="C54">
-        <v>0.08465234051121939</v>
+        <v>0.02716152609520606</v>
       </c>
       <c r="D54">
-        <v>2.07105234051122</v>
+        <v>2.051761526095206</v>
       </c>
       <c r="E54">
-        <v>1.8264</v>
+        <v>1.8646</v>
       </c>
       <c r="F54">
-        <v>1.9864</v>
+        <v>2.0246</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5703,37 +5703,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M54">
-        <v>0.4683931200000001</v>
+        <v>0.4774006800000001</v>
       </c>
       <c r="N54">
-        <v>-0.3653931200000002</v>
+        <v>-0.3744006800000003</v>
       </c>
       <c r="O54">
-        <v>-0.06942469280000003</v>
+        <v>-0.07113612920000005</v>
       </c>
       <c r="P54">
-        <v>-0.2959684272000002</v>
+        <v>-0.3032645508000002</v>
       </c>
       <c r="Q54">
-        <v>0.3730315727999999</v>
+        <v>0.3657354491999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.168416775461536</v>
+        <v>0.1710256430245474</v>
       </c>
       <c r="T54">
-        <v>2.245769303810926</v>
+        <v>2.293551629423925</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04178114315598823</v>
+        <v>0.04099281970021486</v>
       </c>
       <c r="W54">
-        <v>0.225948006443818</v>
+        <v>0.2261338931146893</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2199007534525697</v>
+        <v>0.2157516826327098</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2002330155723226</v>
+        <v>0.2021330155723227</v>
       </c>
       <c r="C55">
-        <v>0.02716152609520606</v>
+        <v>-0.02997323623437698</v>
       </c>
       <c r="D55">
-        <v>2.051761526095206</v>
+        <v>2.032826763765623</v>
       </c>
       <c r="E55">
-        <v>1.8646</v>
+        <v>1.9028</v>
       </c>
       <c r="F55">
-        <v>2.0246</v>
+        <v>2.0628</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5785,37 +5785,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M55">
-        <v>0.4774006800000001</v>
+        <v>0.48640824</v>
       </c>
       <c r="N55">
-        <v>-0.3744006800000003</v>
+        <v>-0.3834082400000002</v>
       </c>
       <c r="O55">
-        <v>-0.07113612920000005</v>
+        <v>-0.07284756560000004</v>
       </c>
       <c r="P55">
-        <v>-0.3032645508000002</v>
+        <v>-0.3105606744000001</v>
       </c>
       <c r="Q55">
-        <v>0.3657354491999998</v>
+        <v>0.3584393255999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1710256430245474</v>
+        <v>0.1737479396120376</v>
       </c>
       <c r="T55">
-        <v>2.293551629423925</v>
+        <v>2.34341144745488</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04099281970021486</v>
+        <v>0.04023369340947015</v>
       </c>
       <c r="W55">
-        <v>0.2261338931146893</v>
+        <v>0.226312895094047</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2157516826327098</v>
+        <v>0.2117562811024745</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2021330155723227</v>
+        <v>0.2040330155723226</v>
       </c>
       <c r="C56">
-        <v>-0.02997323623437698</v>
+        <v>-0.08676171386109788</v>
       </c>
       <c r="D56">
-        <v>2.032826763765623</v>
+        <v>2.014238286138903</v>
       </c>
       <c r="E56">
-        <v>1.9028</v>
+        <v>1.941000000000001</v>
       </c>
       <c r="F56">
-        <v>2.0628</v>
+        <v>2.101</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5867,37 +5867,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M56">
-        <v>0.48640824</v>
+        <v>0.4954158000000001</v>
       </c>
       <c r="N56">
-        <v>-0.3834082400000002</v>
+        <v>-0.3924158000000003</v>
       </c>
       <c r="O56">
-        <v>-0.07284756560000004</v>
+        <v>-0.07455900200000005</v>
       </c>
       <c r="P56">
-        <v>-0.3105606744000001</v>
+        <v>-0.3178567980000002</v>
       </c>
       <c r="Q56">
-        <v>0.3584393255999999</v>
+        <v>0.3511432019999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1737479396120376</v>
+        <v>0.1765912271589718</v>
       </c>
       <c r="T56">
-        <v>2.34341144745488</v>
+        <v>2.395487257398322</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04023369340947015</v>
+        <v>0.03950217171111614</v>
       </c>
       <c r="W56">
-        <v>0.226312895094047</v>
+        <v>0.2264853879105188</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2117562811024745</v>
+        <v>0.2079061669006113</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2040330155723226</v>
+        <v>0.2059330155723226</v>
       </c>
       <c r="C57">
-        <v>-0.08676171386109788</v>
+        <v>-0.1432133201479671</v>
       </c>
       <c r="D57">
-        <v>2.014238286138903</v>
+        <v>1.995986679852033</v>
       </c>
       <c r="E57">
-        <v>1.941000000000001</v>
+        <v>1.9792</v>
       </c>
       <c r="F57">
-        <v>2.101</v>
+        <v>2.1392</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5949,37 +5949,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M57">
-        <v>0.4954158000000001</v>
+        <v>0.5044233600000001</v>
       </c>
       <c r="N57">
-        <v>-0.3924158000000003</v>
+        <v>-0.4014233600000002</v>
       </c>
       <c r="O57">
-        <v>-0.07455900200000005</v>
+        <v>-0.07627043840000004</v>
       </c>
       <c r="P57">
-        <v>-0.3178567980000002</v>
+        <v>-0.3251529216000002</v>
       </c>
       <c r="Q57">
-        <v>0.3511432019999998</v>
+        <v>0.3438470783999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1765912271589718</v>
+        <v>0.1795637550489484</v>
       </c>
       <c r="T57">
-        <v>2.395487257398322</v>
+        <v>2.44993014961192</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03950217171111614</v>
+        <v>0.03879677578770335</v>
       </c>
       <c r="W57">
-        <v>0.2264853879105188</v>
+        <v>0.2266517202692596</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2079061669006113</v>
+        <v>0.204193556777386</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2059330155723226</v>
+        <v>0.2078330155723226</v>
       </c>
       <c r="C58">
-        <v>-0.1432133201479671</v>
+        <v>-0.1993371303328322</v>
       </c>
       <c r="D58">
-        <v>1.995986679852033</v>
+        <v>1.978062869667168</v>
       </c>
       <c r="E58">
-        <v>1.9792</v>
+        <v>2.0174</v>
       </c>
       <c r="F58">
-        <v>2.1392</v>
+        <v>2.1774</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6031,37 +6031,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M58">
-        <v>0.5044233600000001</v>
+        <v>0.5134309200000001</v>
       </c>
       <c r="N58">
-        <v>-0.4014233600000002</v>
+        <v>-0.4104309200000003</v>
       </c>
       <c r="O58">
-        <v>-0.07627043840000004</v>
+        <v>-0.07798187480000005</v>
       </c>
       <c r="P58">
-        <v>-0.3251529216000002</v>
+        <v>-0.3324490452000002</v>
       </c>
       <c r="Q58">
-        <v>0.3438470783999998</v>
+        <v>0.3365509547999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1795637550489484</v>
+        <v>0.1826745400500867</v>
       </c>
       <c r="T58">
-        <v>2.44993014961192</v>
+        <v>2.506905269370337</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03879677578770335</v>
+        <v>0.0381161305984454</v>
       </c>
       <c r="W58">
-        <v>0.2266517202692596</v>
+        <v>0.2268122164048866</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.204193556777386</v>
+        <v>0.2006112136760284</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2078330155723226</v>
+        <v>0.2097330155723227</v>
       </c>
       <c r="C59">
-        <v>-0.1993371303328322</v>
+        <v>-0.2551418965749468</v>
       </c>
       <c r="D59">
-        <v>1.978062869667168</v>
+        <v>1.960458103425053</v>
       </c>
       <c r="E59">
-        <v>2.0174</v>
+        <v>2.0556</v>
       </c>
       <c r="F59">
-        <v>2.1774</v>
+        <v>2.2156</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6113,37 +6113,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M59">
-        <v>0.5134309200000001</v>
+        <v>0.52243848</v>
       </c>
       <c r="N59">
-        <v>-0.4104309200000003</v>
+        <v>-0.4194384800000002</v>
       </c>
       <c r="O59">
-        <v>-0.07798187480000005</v>
+        <v>-0.07969331120000003</v>
       </c>
       <c r="P59">
-        <v>-0.3324490452000002</v>
+        <v>-0.3397451688000002</v>
       </c>
       <c r="Q59">
-        <v>0.3365509547999999</v>
+        <v>0.3292548311999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1826745400500867</v>
+        <v>0.1859334576703269</v>
       </c>
       <c r="T59">
-        <v>2.506905269370337</v>
+        <v>2.566593490069631</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0381161305984454</v>
+        <v>0.03745895593295497</v>
       </c>
       <c r="W59">
-        <v>0.2268122164048866</v>
+        <v>0.2269671781910092</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2006112136760284</v>
+        <v>0.1971523996471314</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2097330155723226</v>
+        <v>0.2116330155723226</v>
       </c>
       <c r="C60">
-        <v>-0.2551418965749463</v>
+        <v>-0.3106360622051536</v>
       </c>
       <c r="D60">
-        <v>1.960458103425053</v>
+        <v>1.943163937794846</v>
       </c>
       <c r="E60">
-        <v>2.0556</v>
+        <v>2.0938</v>
       </c>
       <c r="F60">
-        <v>2.2156</v>
+        <v>2.2538</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6195,37 +6195,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M60">
-        <v>0.5224384799999999</v>
+        <v>0.5314460400000001</v>
       </c>
       <c r="N60">
-        <v>-0.4194384800000001</v>
+        <v>-0.4284460400000002</v>
       </c>
       <c r="O60">
-        <v>-0.07969331120000001</v>
+        <v>-0.08140474760000004</v>
       </c>
       <c r="P60">
-        <v>-0.3397451688000001</v>
+        <v>-0.3470412924000001</v>
       </c>
       <c r="Q60">
-        <v>0.3292548312</v>
+        <v>0.3219587075999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1859334576703268</v>
+        <v>0.1893513468817982</v>
       </c>
       <c r="T60">
-        <v>2.566593490069629</v>
+        <v>2.62919333129084</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03745895593295497</v>
+        <v>0.03682405837476928</v>
       </c>
       <c r="W60">
-        <v>0.2269671781910092</v>
+        <v>0.2271168870352294</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1971523996471314</v>
+        <v>0.1938108335514173</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2116330155723226</v>
+        <v>0.2135330155723226</v>
       </c>
       <c r="C61">
-        <v>-0.3106360622051536</v>
+        <v>-0.365827775228404</v>
       </c>
       <c r="D61">
-        <v>1.943163937794846</v>
+        <v>1.926172224771596</v>
       </c>
       <c r="E61">
-        <v>2.0938</v>
+        <v>2.132</v>
       </c>
       <c r="F61">
-        <v>2.2538</v>
+        <v>2.292</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6277,37 +6277,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M61">
-        <v>0.5314460400000001</v>
+        <v>0.5404536000000001</v>
       </c>
       <c r="N61">
-        <v>-0.4284460400000002</v>
+        <v>-0.4374536000000002</v>
       </c>
       <c r="O61">
-        <v>-0.08140474760000004</v>
+        <v>-0.08311618400000004</v>
       </c>
       <c r="P61">
-        <v>-0.3470412924000001</v>
+        <v>-0.3543374160000002</v>
       </c>
       <c r="Q61">
-        <v>0.3219587075999999</v>
+        <v>0.3146625839999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1893513468817982</v>
+        <v>0.1929401305538432</v>
       </c>
       <c r="T61">
-        <v>2.62919333129084</v>
+        <v>2.694923164573112</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03682405837476928</v>
+        <v>0.03621032406852313</v>
       </c>
       <c r="W61">
-        <v>0.2271168870352294</v>
+        <v>0.2272616055846423</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1938108335514173</v>
+        <v>0.190580652992227</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2135330155723226</v>
+        <v>0.2154330155723226</v>
       </c>
       <c r="C62">
-        <v>-0.365827775228404</v>
+        <v>-0.4207249011240002</v>
       </c>
       <c r="D62">
-        <v>1.926172224771596</v>
+        <v>1.909475098876</v>
       </c>
       <c r="E62">
-        <v>2.132</v>
+        <v>2.1702</v>
       </c>
       <c r="F62">
-        <v>2.292</v>
+        <v>2.3302</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6359,37 +6359,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M62">
-        <v>0.5404536000000001</v>
+        <v>0.54946116</v>
       </c>
       <c r="N62">
-        <v>-0.4374536000000002</v>
+        <v>-0.4464611600000001</v>
       </c>
       <c r="O62">
-        <v>-0.08311618400000004</v>
+        <v>-0.08482762040000003</v>
       </c>
       <c r="P62">
-        <v>-0.3543374160000002</v>
+        <v>-0.3616335396000001</v>
       </c>
       <c r="Q62">
-        <v>0.3146625839999999</v>
+        <v>0.3073664603999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1929401305538432</v>
+        <v>0.1967129544141981</v>
       </c>
       <c r="T62">
-        <v>2.694923164573112</v>
+        <v>2.764023758536525</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03621032406852313</v>
+        <v>0.03561671219854735</v>
       </c>
       <c r="W62">
-        <v>0.2272616055846423</v>
+        <v>0.2274015792635825</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.190580652992227</v>
+        <v>0.1874563799923544</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2154330155723226</v>
+        <v>0.2173330155723226</v>
       </c>
       <c r="C63">
-        <v>-0.4207249011240002</v>
+        <v>-0.4753350349858008</v>
       </c>
       <c r="D63">
-        <v>1.909475098876</v>
+        <v>1.8930649650142</v>
       </c>
       <c r="E63">
-        <v>2.1702</v>
+        <v>2.2084</v>
       </c>
       <c r="F63">
-        <v>2.3302</v>
+        <v>2.3684</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6441,37 +6441,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M63">
-        <v>0.54946116</v>
+        <v>0.5584687200000001</v>
       </c>
       <c r="N63">
-        <v>-0.4464611600000001</v>
+        <v>-0.4554687200000003</v>
       </c>
       <c r="O63">
-        <v>-0.08482762040000003</v>
+        <v>-0.08653905680000006</v>
       </c>
       <c r="P63">
-        <v>-0.3616335396000001</v>
+        <v>-0.3689296632000002</v>
       </c>
       <c r="Q63">
-        <v>0.3073664603999999</v>
+        <v>0.3000703367999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1967129544141981</v>
+        <v>0.2006843479514139</v>
       </c>
       <c r="T63">
-        <v>2.764023758536525</v>
+        <v>2.836761225866433</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03561671219854735</v>
+        <v>0.03504224909857077</v>
       </c>
       <c r="W63">
-        <v>0.2274015792635825</v>
+        <v>0.227537037662557</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1874563799923544</v>
+        <v>0.1844328899924778</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2173330155723226</v>
+        <v>0.2192330155723226</v>
       </c>
       <c r="C64">
-        <v>-0.4753350349858008</v>
+        <v>-0.529665513041758</v>
       </c>
       <c r="D64">
-        <v>1.8930649650142</v>
+        <v>1.876934486958242</v>
       </c>
       <c r="E64">
-        <v>2.2084</v>
+        <v>2.2466</v>
       </c>
       <c r="F64">
-        <v>2.3684</v>
+        <v>2.4066</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6523,37 +6523,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M64">
-        <v>0.5584687200000001</v>
+        <v>0.5674762800000001</v>
       </c>
       <c r="N64">
-        <v>-0.4554687200000003</v>
+        <v>-0.4644762800000002</v>
       </c>
       <c r="O64">
-        <v>-0.08653905680000006</v>
+        <v>-0.08825049320000003</v>
       </c>
       <c r="P64">
-        <v>-0.3689296632000002</v>
+        <v>-0.3762257868000002</v>
       </c>
       <c r="Q64">
-        <v>0.3000703367999998</v>
+        <v>0.2927742131999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2006843479514139</v>
+        <v>0.2048704114095602</v>
       </c>
       <c r="T64">
-        <v>2.836761225866433</v>
+        <v>2.913430448187147</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03504224909857077</v>
+        <v>0.03448602292240299</v>
       </c>
       <c r="W64">
-        <v>0.227537037662557</v>
+        <v>0.2276681957948974</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1844328899924778</v>
+        <v>0.181505383802121</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2192330155723226</v>
+        <v>0.2211330155723226</v>
       </c>
       <c r="C65">
-        <v>-0.529665513041758</v>
+        <v>-0.5837234235894924</v>
       </c>
       <c r="D65">
-        <v>1.876934486958242</v>
+        <v>1.861076576410508</v>
       </c>
       <c r="E65">
-        <v>2.2466</v>
+        <v>2.2848</v>
       </c>
       <c r="F65">
-        <v>2.4066</v>
+        <v>2.4448</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6605,37 +6605,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M65">
-        <v>0.5674762800000001</v>
+        <v>0.5764838400000001</v>
       </c>
       <c r="N65">
-        <v>-0.4644762800000002</v>
+        <v>-0.4734838400000002</v>
       </c>
       <c r="O65">
-        <v>-0.08825049320000003</v>
+        <v>-0.08996192960000005</v>
       </c>
       <c r="P65">
-        <v>-0.3762257868000002</v>
+        <v>-0.3835219104000002</v>
       </c>
       <c r="Q65">
-        <v>0.2927742131999999</v>
+        <v>0.2854780895999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2048704114095602</v>
+        <v>0.2092890339487146</v>
       </c>
       <c r="T65">
-        <v>2.913430448187147</v>
+        <v>2.994359071747902</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03448602292240299</v>
+        <v>0.03394717881424043</v>
       </c>
       <c r="W65">
-        <v>0.2276681957948974</v>
+        <v>0.2277952552356021</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.181505383802121</v>
+        <v>0.1786693621802128</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2211330155723226</v>
+        <v>0.2230330155723226</v>
       </c>
       <c r="C66">
-        <v>-0.5837234235894924</v>
+        <v>-0.6375156173821603</v>
       </c>
       <c r="D66">
-        <v>1.861076576410508</v>
+        <v>1.84548438261784</v>
       </c>
       <c r="E66">
-        <v>2.2848</v>
+        <v>2.323</v>
       </c>
       <c r="F66">
-        <v>2.4448</v>
+        <v>2.483</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6687,37 +6687,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M66">
-        <v>0.5764838400000001</v>
+        <v>0.5854914</v>
       </c>
       <c r="N66">
-        <v>-0.4734838400000002</v>
+        <v>-0.4824914000000001</v>
       </c>
       <c r="O66">
-        <v>-0.08996192960000005</v>
+        <v>-0.09167336600000002</v>
       </c>
       <c r="P66">
-        <v>-0.3835219104000002</v>
+        <v>-0.3908180340000001</v>
       </c>
       <c r="Q66">
-        <v>0.2854780895999999</v>
+        <v>0.2781819659999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2092890339487146</v>
+        <v>0.2139601492043922</v>
       </c>
       <c r="T66">
-        <v>2.994359071747902</v>
+        <v>3.079912188083556</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03394717881424043</v>
+        <v>0.03342491452479059</v>
       </c>
       <c r="W66">
-        <v>0.2277952552356021</v>
+        <v>0.2279184051550544</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1786693621802128</v>
+        <v>0.1759206027620557</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2230330155723226</v>
+        <v>0.2249330155723226</v>
       </c>
       <c r="C67">
-        <v>-0.6375156173821603</v>
+        <v>-0.6910487174965745</v>
       </c>
       <c r="D67">
-        <v>1.84548438261784</v>
+        <v>1.830151282503426</v>
       </c>
       <c r="E67">
-        <v>2.323</v>
+        <v>2.3612</v>
       </c>
       <c r="F67">
-        <v>2.483</v>
+        <v>2.5212</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6769,37 +6769,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M67">
-        <v>0.5854914</v>
+        <v>0.5944989600000001</v>
       </c>
       <c r="N67">
-        <v>-0.4824914000000001</v>
+        <v>-0.4914989600000003</v>
       </c>
       <c r="O67">
-        <v>-0.09167336600000002</v>
+        <v>-0.09338480240000005</v>
       </c>
       <c r="P67">
-        <v>-0.3908180340000001</v>
+        <v>-0.3981141576000002</v>
       </c>
       <c r="Q67">
-        <v>0.2781819659999999</v>
+        <v>0.2708858423999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2139601492043922</v>
+        <v>0.2189060359456979</v>
       </c>
       <c r="T67">
-        <v>3.079912188083556</v>
+        <v>3.170497840674249</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03342491452479059</v>
+        <v>0.03291847642593011</v>
       </c>
       <c r="W67">
-        <v>0.2279184051550544</v>
+        <v>0.2280378232587657</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1759206027620557</v>
+        <v>0.1732551390838427</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2249330155723226</v>
+        <v>0.2268330155723227</v>
       </c>
       <c r="C68">
-        <v>-0.6910487174965745</v>
+        <v>-0.7443291287134473</v>
       </c>
       <c r="D68">
-        <v>1.830151282503426</v>
+        <v>1.815070871286553</v>
       </c>
       <c r="E68">
-        <v>2.3612</v>
+        <v>2.3994</v>
       </c>
       <c r="F68">
-        <v>2.5212</v>
+        <v>2.559400000000001</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6851,37 +6851,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M68">
-        <v>0.5944989600000001</v>
+        <v>0.6035065200000002</v>
       </c>
       <c r="N68">
-        <v>-0.4914989600000003</v>
+        <v>-0.5005065200000003</v>
       </c>
       <c r="O68">
-        <v>-0.09338480240000005</v>
+        <v>-0.09509623880000005</v>
       </c>
       <c r="P68">
-        <v>-0.3981141576000002</v>
+        <v>-0.4054102812000002</v>
       </c>
       <c r="Q68">
-        <v>0.2708858423999998</v>
+        <v>0.2635897187999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2189060359456979</v>
+        <v>0.2241516733985978</v>
       </c>
       <c r="T68">
-        <v>3.170497840674249</v>
+        <v>3.266573532815893</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03291847642593011</v>
+        <v>0.03242715588225952</v>
       </c>
       <c r="W68">
-        <v>0.2280378232587657</v>
+        <v>0.2281536766429632</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1732551390838427</v>
+        <v>0.1706692414855764</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2268330155723227</v>
+        <v>0.2287330155723226</v>
       </c>
       <c r="C69">
-        <v>-0.7443291287134473</v>
+        <v>-0.7973630464376658</v>
       </c>
       <c r="D69">
-        <v>1.815070871286553</v>
+        <v>1.800236953562335</v>
       </c>
       <c r="E69">
-        <v>2.3994</v>
+        <v>2.4376</v>
       </c>
       <c r="F69">
-        <v>2.559400000000001</v>
+        <v>2.5976</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6933,37 +6933,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M69">
-        <v>0.6035065200000002</v>
+        <v>0.6125140800000001</v>
       </c>
       <c r="N69">
-        <v>-0.5005065200000003</v>
+        <v>-0.5095140800000002</v>
       </c>
       <c r="O69">
-        <v>-0.09509623880000005</v>
+        <v>-0.09680767520000004</v>
       </c>
       <c r="P69">
-        <v>-0.4054102812000002</v>
+        <v>-0.4127064048000001</v>
       </c>
       <c r="Q69">
-        <v>0.2635897187999998</v>
+        <v>0.2562935951999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2241516733985978</v>
+        <v>0.229725163192304</v>
       </c>
       <c r="T69">
-        <v>3.266573532815893</v>
+        <v>3.36865395571639</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03242715588225952</v>
+        <v>0.03195028594281453</v>
       </c>
       <c r="W69">
-        <v>0.2281536766429632</v>
+        <v>0.2282661225746843</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1706692414855764</v>
+        <v>0.1681593996990238</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2287330155723226</v>
+        <v>0.2306330155723227</v>
       </c>
       <c r="C70">
-        <v>-0.7973630464376658</v>
+        <v>-0.8501564651847036</v>
       </c>
       <c r="D70">
-        <v>1.800236953562335</v>
+        <v>1.785643534815297</v>
       </c>
       <c r="E70">
-        <v>2.4376</v>
+        <v>2.4758</v>
       </c>
       <c r="F70">
-        <v>2.5976</v>
+        <v>2.635800000000001</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7015,37 +7015,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M70">
-        <v>0.6125140800000001</v>
+        <v>0.6215216400000002</v>
       </c>
       <c r="N70">
-        <v>-0.5095140800000002</v>
+        <v>-0.5185216400000003</v>
       </c>
       <c r="O70">
-        <v>-0.09680767520000004</v>
+        <v>-0.09851911160000007</v>
       </c>
       <c r="P70">
-        <v>-0.4127064048000001</v>
+        <v>-0.4200025284000003</v>
       </c>
       <c r="Q70">
-        <v>0.2562935951999999</v>
+        <v>0.2489974715999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.229725163192304</v>
+        <v>0.2356582329727009</v>
       </c>
       <c r="T70">
-        <v>3.36865395571639</v>
+        <v>3.477320212352403</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03195028594281453</v>
+        <v>0.03148723832045489</v>
       </c>
       <c r="W70">
-        <v>0.2282661225746843</v>
+        <v>0.2283753092040368</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1681593996990238</v>
+        <v>0.1657223069497625</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2306330155723227</v>
+        <v>0.2325330155723226</v>
       </c>
       <c r="C71">
-        <v>-0.8501564651847036</v>
+        <v>-0.9027151866575749</v>
       </c>
       <c r="D71">
-        <v>1.785643534815297</v>
+        <v>1.771284813342425</v>
       </c>
       <c r="E71">
-        <v>2.4758</v>
+        <v>2.514</v>
       </c>
       <c r="F71">
-        <v>2.635800000000001</v>
+        <v>2.674</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7097,37 +7097,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M71">
-        <v>0.6215216400000002</v>
+        <v>0.6305292000000001</v>
       </c>
       <c r="N71">
-        <v>-0.5185216400000003</v>
+        <v>-0.5275292000000003</v>
       </c>
       <c r="O71">
-        <v>-0.09851911160000007</v>
+        <v>-0.100230548</v>
       </c>
       <c r="P71">
-        <v>-0.4200025284000003</v>
+        <v>-0.4272986520000002</v>
       </c>
       <c r="Q71">
-        <v>0.2489974715999997</v>
+        <v>0.2417013479999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2356582329727009</v>
+        <v>0.2419868407384576</v>
       </c>
       <c r="T71">
-        <v>3.477320212352403</v>
+        <v>3.593230886097482</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03148723832045489</v>
+        <v>0.03103742063016268</v>
       </c>
       <c r="W71">
-        <v>0.2283753092040368</v>
+        <v>0.2284813762154076</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1657223069497625</v>
+        <v>0.1633548454219088</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2325330155723226</v>
+        <v>0.2344330155723227</v>
       </c>
       <c r="C72">
-        <v>-0.9027151866575749</v>
+        <v>-0.9550448274372256</v>
       </c>
       <c r="D72">
-        <v>1.771284813342425</v>
+        <v>1.757155172562775</v>
       </c>
       <c r="E72">
-        <v>2.514</v>
+        <v>2.5522</v>
       </c>
       <c r="F72">
-        <v>2.674</v>
+        <v>2.712200000000001</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7179,37 +7179,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M72">
-        <v>0.6305292000000001</v>
+        <v>0.6395367600000001</v>
       </c>
       <c r="N72">
-        <v>-0.5275292000000003</v>
+        <v>-0.5365367600000003</v>
       </c>
       <c r="O72">
-        <v>-0.100230548</v>
+        <v>-0.1019419844000001</v>
       </c>
       <c r="P72">
-        <v>-0.4272986520000002</v>
+        <v>-0.4345947756000002</v>
       </c>
       <c r="Q72">
-        <v>0.2417013479999998</v>
+        <v>0.2344052243999998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2419868407384576</v>
+        <v>0.2487519042121976</v>
       </c>
       <c r="T72">
-        <v>3.593230886097482</v>
+        <v>3.717135399411189</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03103742063016268</v>
+        <v>0.03060027386072377</v>
       </c>
       <c r="W72">
-        <v>0.2284813762154076</v>
+        <v>0.2285844554236414</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1633548454219088</v>
+        <v>0.1610540729511777</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2344330155723227</v>
+        <v>0.2363330155723226</v>
       </c>
       <c r="C73">
-        <v>-0.9550448274372252</v>
+        <v>-1.007150826307736</v>
       </c>
       <c r="D73">
-        <v>1.757155172562775</v>
+        <v>1.743249173692264</v>
       </c>
       <c r="E73">
-        <v>2.5522</v>
+        <v>2.5904</v>
       </c>
       <c r="F73">
-        <v>2.7122</v>
+        <v>2.7504</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7261,37 +7261,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M73">
-        <v>0.63953676</v>
+        <v>0.6485443200000001</v>
       </c>
       <c r="N73">
-        <v>-0.5365367600000002</v>
+        <v>-0.5455443200000002</v>
       </c>
       <c r="O73">
-        <v>-0.1019419844</v>
+        <v>-0.1036534208</v>
       </c>
       <c r="P73">
-        <v>-0.4345947756000001</v>
+        <v>-0.4418908992000001</v>
       </c>
       <c r="Q73">
-        <v>0.2344052243999999</v>
+        <v>0.2271091007999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2487519042121975</v>
+        <v>0.2560001865054902</v>
       </c>
       <c r="T73">
-        <v>3.717135399411188</v>
+        <v>3.849890235104444</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03060027386072378</v>
+        <v>0.03017527005710261</v>
       </c>
       <c r="W73">
-        <v>0.2285844554236414</v>
+        <v>0.2286846713205352</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1610540729511778</v>
+        <v>0.1588172108268558</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2363330155723226</v>
+        <v>0.2382330155723226</v>
       </c>
       <c r="C74">
-        <v>-1.007150826307736</v>
+        <v>-1.059038451236449</v>
       </c>
       <c r="D74">
-        <v>1.743249173692264</v>
+        <v>1.729561548763551</v>
       </c>
       <c r="E74">
-        <v>2.5904</v>
+        <v>2.6286</v>
       </c>
       <c r="F74">
-        <v>2.7504</v>
+        <v>2.7886</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7343,37 +7343,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M74">
-        <v>0.6485443200000001</v>
+        <v>0.6575518800000001</v>
       </c>
       <c r="N74">
-        <v>-0.5455443200000002</v>
+        <v>-0.5545518800000002</v>
       </c>
       <c r="O74">
-        <v>-0.1036534208</v>
+        <v>-0.1053648572</v>
       </c>
       <c r="P74">
-        <v>-0.4418908992000001</v>
+        <v>-0.4491870228000002</v>
       </c>
       <c r="Q74">
-        <v>0.2271091007999999</v>
+        <v>0.2198129771999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2560001865054902</v>
+        <v>0.2637853785982862</v>
       </c>
       <c r="T74">
-        <v>3.849890235104444</v>
+        <v>3.992478762330535</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03017527005710261</v>
+        <v>0.02976191019330669</v>
       </c>
       <c r="W74">
-        <v>0.2286846713205352</v>
+        <v>0.2287821415764183</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1588172108268558</v>
+        <v>0.156641632596351</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2382330155723226</v>
+        <v>0.2401330155723226</v>
       </c>
       <c r="C75">
-        <v>-1.059038451236449</v>
+        <v>-1.1107128060278</v>
       </c>
       <c r="D75">
-        <v>1.729561548763551</v>
+        <v>1.7160871939722</v>
       </c>
       <c r="E75">
-        <v>2.6286</v>
+        <v>2.6668</v>
       </c>
       <c r="F75">
-        <v>2.7886</v>
+        <v>2.8268</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7425,37 +7425,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M75">
-        <v>0.6575518800000001</v>
+        <v>0.66655944</v>
       </c>
       <c r="N75">
-        <v>-0.5545518800000002</v>
+        <v>-0.5635594400000001</v>
       </c>
       <c r="O75">
-        <v>-0.1053648572</v>
+        <v>-0.1070762936</v>
       </c>
       <c r="P75">
-        <v>-0.4491870228000002</v>
+        <v>-0.4564831464000001</v>
       </c>
       <c r="Q75">
-        <v>0.2198129771999999</v>
+        <v>0.2125168535999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2637853785982862</v>
+        <v>0.2721694316212971</v>
       </c>
       <c r="T75">
-        <v>3.992478762330535</v>
+        <v>4.146035637804786</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02976191019330669</v>
+        <v>0.02935972221772146</v>
       </c>
       <c r="W75">
-        <v>0.2287821415764183</v>
+        <v>0.2288769775010613</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.156641632596351</v>
+        <v>0.1545248537774814</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2401330155723226</v>
+        <v>0.2420330155723226</v>
       </c>
       <c r="C76">
-        <v>-1.1107128060278</v>
+        <v>-1.162178836668543</v>
       </c>
       <c r="D76">
-        <v>1.7160871939722</v>
+        <v>1.702821163331457</v>
       </c>
       <c r="E76">
-        <v>2.6668</v>
+        <v>2.705</v>
       </c>
       <c r="F76">
-        <v>2.8268</v>
+        <v>2.865</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7507,37 +7507,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M76">
-        <v>0.66655944</v>
+        <v>0.675567</v>
       </c>
       <c r="N76">
-        <v>-0.5635594400000001</v>
+        <v>-0.5725670000000002</v>
       </c>
       <c r="O76">
-        <v>-0.1070762936</v>
+        <v>-0.10878773</v>
       </c>
       <c r="P76">
-        <v>-0.4564831464000001</v>
+        <v>-0.4637792700000001</v>
       </c>
       <c r="Q76">
-        <v>0.2125168535999999</v>
+        <v>0.2052207299999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2721694316212971</v>
+        <v>0.2812242088861491</v>
       </c>
       <c r="T76">
-        <v>4.146035637804786</v>
+        <v>4.311877063316978</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02935972221772146</v>
+        <v>0.02896825925481851</v>
       </c>
       <c r="W76">
-        <v>0.2288769775010613</v>
+        <v>0.2289692844677138</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1545248537774814</v>
+        <v>0.1524645223937816</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2420330155723226</v>
+        <v>0.2439330155723226</v>
       </c>
       <c r="C77">
-        <v>-1.162178836668543</v>
+        <v>-1.213441337380921</v>
       </c>
       <c r="D77">
-        <v>1.702821163331457</v>
+        <v>1.68975866261908</v>
       </c>
       <c r="E77">
-        <v>2.705</v>
+        <v>2.7432</v>
       </c>
       <c r="F77">
-        <v>2.865</v>
+        <v>2.9032</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7589,37 +7589,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M77">
-        <v>0.675567</v>
+        <v>0.6845745600000002</v>
       </c>
       <c r="N77">
-        <v>-0.5725670000000002</v>
+        <v>-0.5815745600000003</v>
       </c>
       <c r="O77">
-        <v>-0.10878773</v>
+        <v>-0.1104991664000001</v>
       </c>
       <c r="P77">
-        <v>-0.4637792700000001</v>
+        <v>-0.4710753936000002</v>
       </c>
       <c r="Q77">
-        <v>0.2052207299999999</v>
+        <v>0.1979246063999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2812242088861491</v>
+        <v>0.291033550923072</v>
       </c>
       <c r="T77">
-        <v>4.311877063316978</v>
+        <v>4.491538607621853</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02896825925481851</v>
+        <v>0.02858709794883405</v>
       </c>
       <c r="W77">
-        <v>0.2289692844677138</v>
+        <v>0.2290591623036649</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1524645223937816</v>
+        <v>0.1504584102570213</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2439330155723226</v>
+        <v>0.2458330155723226</v>
       </c>
       <c r="C78">
-        <v>-1.213441337380921</v>
+        <v>-1.264504956399352</v>
       </c>
       <c r="D78">
-        <v>1.68975866261908</v>
+        <v>1.676895043600648</v>
       </c>
       <c r="E78">
-        <v>2.7432</v>
+        <v>2.7814</v>
       </c>
       <c r="F78">
-        <v>2.9032</v>
+        <v>2.9414</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7671,37 +7671,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M78">
-        <v>0.6845745600000002</v>
+        <v>0.6935821200000001</v>
       </c>
       <c r="N78">
-        <v>-0.5815745600000003</v>
+        <v>-0.5905821200000002</v>
       </c>
       <c r="O78">
-        <v>-0.1104991664000001</v>
+        <v>-0.1122106028</v>
       </c>
       <c r="P78">
-        <v>-0.4710753936000002</v>
+        <v>-0.4783715172000002</v>
       </c>
       <c r="Q78">
-        <v>0.1979246063999998</v>
+        <v>0.1906284827999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.291033550923072</v>
+        <v>0.3016958792240751</v>
       </c>
       <c r="T78">
-        <v>4.491538607621853</v>
+        <v>4.68682289490976</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02858709794883405</v>
+        <v>0.02821583693651153</v>
       </c>
       <c r="W78">
-        <v>0.2290591623036649</v>
+        <v>0.2291467056503706</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1504584102570213</v>
+        <v>0.1485044049290081</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2458330155723226</v>
+        <v>0.2477330155723226</v>
       </c>
       <c r="C79">
-        <v>-1.264504956399352</v>
+        <v>-1.315374201485249</v>
       </c>
       <c r="D79">
-        <v>1.676895043600648</v>
+        <v>1.664225798514751</v>
       </c>
       <c r="E79">
-        <v>2.7814</v>
+        <v>2.8196</v>
       </c>
       <c r="F79">
-        <v>2.9414</v>
+        <v>2.9796</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7753,37 +7753,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M79">
-        <v>0.6935821200000001</v>
+        <v>0.7025896800000001</v>
       </c>
       <c r="N79">
-        <v>-0.5905821200000002</v>
+        <v>-0.5995896800000002</v>
       </c>
       <c r="O79">
-        <v>-0.1122106028</v>
+        <v>-0.1139220392</v>
       </c>
       <c r="P79">
-        <v>-0.4783715172000002</v>
+        <v>-0.4856676408000002</v>
       </c>
       <c r="Q79">
-        <v>0.1906284827999999</v>
+        <v>0.1833323591999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3016958792240751</v>
+        <v>0.3133275100978967</v>
       </c>
       <c r="T79">
-        <v>4.68682289490976</v>
+        <v>4.89986029922384</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02821583693651153</v>
+        <v>0.02785409543732548</v>
       </c>
       <c r="W79">
-        <v>0.2291467056503706</v>
+        <v>0.2292320042958786</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1485044049290081</v>
+        <v>0.1466005023017131</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2477330155723226</v>
+        <v>0.2496330155723226</v>
       </c>
       <c r="C80">
-        <v>-1.315374201485249</v>
+        <v>-1.366053445193724</v>
       </c>
       <c r="D80">
-        <v>1.664225798514751</v>
+        <v>1.651746554806276</v>
       </c>
       <c r="E80">
-        <v>2.8196</v>
+        <v>2.8578</v>
       </c>
       <c r="F80">
-        <v>2.9796</v>
+        <v>3.0178</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7835,37 +7835,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M80">
-        <v>0.7025896800000001</v>
+        <v>0.7115972400000001</v>
       </c>
       <c r="N80">
-        <v>-0.5995896800000002</v>
+        <v>-0.6085972400000003</v>
       </c>
       <c r="O80">
-        <v>-0.1139220392</v>
+        <v>-0.1156334756</v>
       </c>
       <c r="P80">
-        <v>-0.4856676408000002</v>
+        <v>-0.4929637644000002</v>
       </c>
       <c r="Q80">
-        <v>0.1833323591999999</v>
+        <v>0.1760362355999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3133275100978967</v>
+        <v>0.3260669153406538</v>
       </c>
       <c r="T80">
-        <v>4.89986029922384</v>
+        <v>5.133186980139262</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02785409543732548</v>
+        <v>0.02750151195077706</v>
       </c>
       <c r="W80">
-        <v>0.2292320042958786</v>
+        <v>0.2293151434820068</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1466005023017131</v>
+        <v>0.1447447997409319</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2496330155723226</v>
+        <v>0.2515330155723227</v>
       </c>
       <c r="C81">
-        <v>-1.366053445193724</v>
+        <v>-1.416546929905102</v>
       </c>
       <c r="D81">
-        <v>1.651746554806276</v>
+        <v>1.639453070094899</v>
       </c>
       <c r="E81">
-        <v>2.8578</v>
+        <v>2.896</v>
       </c>
       <c r="F81">
-        <v>3.0178</v>
+        <v>3.056</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7917,37 +7917,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M81">
-        <v>0.7115972400000001</v>
+        <v>0.7206048000000002</v>
       </c>
       <c r="N81">
-        <v>-0.6085972400000003</v>
+        <v>-0.6176048000000003</v>
       </c>
       <c r="O81">
-        <v>-0.1156334756</v>
+        <v>-0.1173449120000001</v>
       </c>
       <c r="P81">
-        <v>-0.4929637644000002</v>
+        <v>-0.5002598880000002</v>
       </c>
       <c r="Q81">
-        <v>0.1760362355999998</v>
+        <v>0.1687401119999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3260669153406538</v>
+        <v>0.3400802611076865</v>
       </c>
       <c r="T81">
-        <v>5.133186980139262</v>
+        <v>5.389846329146224</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02750151195077706</v>
+        <v>0.02715774305139235</v>
       </c>
       <c r="W81">
-        <v>0.2293151434820068</v>
+        <v>0.2293962041884817</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1447447997409319</v>
+        <v>0.1429354897441703</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2515330155723227</v>
+        <v>0.2534330155723227</v>
       </c>
       <c r="C82">
-        <v>-1.416546929905102</v>
+        <v>-1.466858772633402</v>
       </c>
       <c r="D82">
-        <v>1.639453070094899</v>
+        <v>1.627341227366598</v>
       </c>
       <c r="E82">
-        <v>2.896</v>
+        <v>2.9342</v>
       </c>
       <c r="F82">
-        <v>3.056</v>
+        <v>3.0942</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7999,37 +7999,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M82">
-        <v>0.7206048000000002</v>
+        <v>0.7296123600000001</v>
       </c>
       <c r="N82">
-        <v>-0.6176048000000003</v>
+        <v>-0.6266123600000002</v>
       </c>
       <c r="O82">
-        <v>-0.1173449120000001</v>
+        <v>-0.1190563484</v>
       </c>
       <c r="P82">
-        <v>-0.5002598880000002</v>
+        <v>-0.5075560116000002</v>
       </c>
       <c r="Q82">
-        <v>0.1687401119999998</v>
+        <v>0.1614439883999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3400802611076865</v>
+        <v>0.3555686959028278</v>
       </c>
       <c r="T82">
-        <v>5.389846329146224</v>
+        <v>5.673522451732867</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02715774305139235</v>
+        <v>0.0268224622729801</v>
       </c>
       <c r="W82">
-        <v>0.2293962041884817</v>
+        <v>0.2294752633960313</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1429354897441703</v>
+        <v>0.1411708540683163</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2534330155723227</v>
+        <v>0.2553330155723226</v>
       </c>
       <c r="C83">
-        <v>-1.466858772633402</v>
+        <v>-1.516992969623244</v>
       </c>
       <c r="D83">
-        <v>1.627341227366598</v>
+        <v>1.615407030376756</v>
       </c>
       <c r="E83">
-        <v>2.9342</v>
+        <v>2.9724</v>
       </c>
       <c r="F83">
-        <v>3.0942</v>
+        <v>3.132400000000001</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8081,37 +8081,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M83">
-        <v>0.7296123600000001</v>
+        <v>0.7386199200000002</v>
       </c>
       <c r="N83">
-        <v>-0.6266123600000002</v>
+        <v>-0.6356199200000003</v>
       </c>
       <c r="O83">
-        <v>-0.1190563484</v>
+        <v>-0.1207677848000001</v>
       </c>
       <c r="P83">
-        <v>-0.5075560116000002</v>
+        <v>-0.5148521352000003</v>
       </c>
       <c r="Q83">
-        <v>0.1614439883999998</v>
+        <v>0.1541478647999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3555686959028278</v>
+        <v>0.3727780678974293</v>
       </c>
       <c r="T83">
-        <v>5.673522451732867</v>
+        <v>5.988718143495804</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0268224622729801</v>
+        <v>0.02649535907452912</v>
       </c>
       <c r="W83">
-        <v>0.2294752633960313</v>
+        <v>0.229552394330226</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1411708540683163</v>
+        <v>0.1394492582869954</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2553330155723226</v>
+        <v>0.2572330155723226</v>
       </c>
       <c r="C84">
-        <v>-1.516992969623244</v>
+        <v>-1.566953400745953</v>
       </c>
       <c r="D84">
-        <v>1.615407030376756</v>
+        <v>1.603646599254047</v>
       </c>
       <c r="E84">
-        <v>2.9724</v>
+        <v>3.0106</v>
       </c>
       <c r="F84">
-        <v>3.132400000000001</v>
+        <v>3.1706</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8163,37 +8163,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M84">
-        <v>0.7386199200000002</v>
+        <v>0.7476274800000001</v>
       </c>
       <c r="N84">
-        <v>-0.6356199200000003</v>
+        <v>-0.6446274800000003</v>
       </c>
       <c r="O84">
-        <v>-0.1207677848000001</v>
+        <v>-0.1224792212</v>
       </c>
       <c r="P84">
-        <v>-0.5148521352000003</v>
+        <v>-0.5221482588000002</v>
       </c>
       <c r="Q84">
-        <v>0.1541478647999998</v>
+        <v>0.1468517411999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3727780678974293</v>
+        <v>0.3920120718913959</v>
       </c>
       <c r="T84">
-        <v>5.988718143495804</v>
+        <v>6.3409956813485</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02649535907452912</v>
+        <v>0.0261761378808601</v>
       </c>
       <c r="W84">
-        <v>0.229552394330226</v>
+        <v>0.2296276666876932</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1394492582869954</v>
+        <v>0.1377691467413689</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2572330155723226</v>
+        <v>0.2591330155723227</v>
       </c>
       <c r="C85">
-        <v>-1.566953400745953</v>
+        <v>-1.616743833705026</v>
       </c>
       <c r="D85">
-        <v>1.603646599254047</v>
+        <v>1.592056166294975</v>
       </c>
       <c r="E85">
-        <v>3.0106</v>
+        <v>3.0488</v>
       </c>
       <c r="F85">
-        <v>3.1706</v>
+        <v>3.208800000000001</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8245,37 +8245,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M85">
-        <v>0.7476274800000001</v>
+        <v>0.7566350400000001</v>
       </c>
       <c r="N85">
-        <v>-0.6446274800000003</v>
+        <v>-0.6536350400000003</v>
       </c>
       <c r="O85">
-        <v>-0.1224792212</v>
+        <v>-0.1241906576000001</v>
       </c>
       <c r="P85">
-        <v>-0.5221482588000002</v>
+        <v>-0.5294443824000002</v>
       </c>
       <c r="Q85">
-        <v>0.1468517411999999</v>
+        <v>0.1395556175999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3920120718913959</v>
+        <v>0.4136503263846081</v>
       </c>
       <c r="T85">
-        <v>6.3409956813485</v>
+        <v>6.737307911432782</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0261761378808601</v>
+        <v>0.02586451719180223</v>
       </c>
       <c r="W85">
-        <v>0.2296276666876932</v>
+        <v>0.229701146846173</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1377691467413689</v>
+        <v>0.1361290378515907</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2591330155723226</v>
+        <v>0.2610330155723227</v>
       </c>
       <c r="C86">
-        <v>-1.616743833705025</v>
+        <v>-1.666367928060537</v>
       </c>
       <c r="D86">
-        <v>1.592056166294975</v>
+        <v>1.580632071939464</v>
       </c>
       <c r="E86">
-        <v>3.0488</v>
+        <v>3.087</v>
       </c>
       <c r="F86">
-        <v>3.2088</v>
+        <v>3.247</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8327,37 +8327,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M86">
-        <v>0.75663504</v>
+        <v>0.7656426000000001</v>
       </c>
       <c r="N86">
-        <v>-0.6536350400000002</v>
+        <v>-0.6626426000000002</v>
       </c>
       <c r="O86">
-        <v>-0.1241906576</v>
+        <v>-0.125902094</v>
       </c>
       <c r="P86">
-        <v>-0.5294443824000001</v>
+        <v>-0.5367405060000001</v>
       </c>
       <c r="Q86">
-        <v>0.1395556175999999</v>
+        <v>0.1322594939999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4136503263846079</v>
+        <v>0.4381736814769152</v>
       </c>
       <c r="T86">
-        <v>6.737307911432778</v>
+        <v>7.186461772194964</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02586451719180224</v>
+        <v>0.02556022875425162</v>
       </c>
       <c r="W86">
-        <v>0.229701146846173</v>
+        <v>0.2297728980597475</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1361290378515907</v>
+        <v>0.1345275197592191</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2610330155723227</v>
+        <v>0.2629330155723226</v>
       </c>
       <c r="C87">
-        <v>-1.666367928060537</v>
+        <v>-1.715829239081514</v>
       </c>
       <c r="D87">
-        <v>1.580632071939464</v>
+        <v>1.569370760918486</v>
       </c>
       <c r="E87">
-        <v>3.087</v>
+        <v>3.1252</v>
       </c>
       <c r="F87">
-        <v>3.247</v>
+        <v>3.2852</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8409,37 +8409,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M87">
-        <v>0.7656426000000001</v>
+        <v>0.7746501600000001</v>
       </c>
       <c r="N87">
-        <v>-0.6626426000000002</v>
+        <v>-0.6716501600000002</v>
       </c>
       <c r="O87">
-        <v>-0.125902094</v>
+        <v>-0.1276135304</v>
       </c>
       <c r="P87">
-        <v>-0.5367405060000001</v>
+        <v>-0.5440366296000002</v>
       </c>
       <c r="Q87">
-        <v>0.1322594939999999</v>
+        <v>0.1249633703999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4381736814769152</v>
+        <v>0.4662003730109806</v>
       </c>
       <c r="T87">
-        <v>7.186461772194964</v>
+        <v>7.69978047020889</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02556022875425162</v>
+        <v>0.02526301679199288</v>
       </c>
       <c r="W87">
-        <v>0.2297728980597475</v>
+        <v>0.2298429806404481</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1345275197592191</v>
+        <v>0.1329632462736468</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2629330155723226</v>
+        <v>0.2648330155723226</v>
       </c>
       <c r="C88">
-        <v>-1.715829239081514</v>
+        <v>-1.765131221434796</v>
       </c>
       <c r="D88">
-        <v>1.569370760918486</v>
+        <v>1.558268778565205</v>
       </c>
       <c r="E88">
-        <v>3.1252</v>
+        <v>3.1634</v>
       </c>
       <c r="F88">
-        <v>3.2852</v>
+        <v>3.3234</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8491,37 +8491,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M88">
-        <v>0.7746501600000001</v>
+        <v>0.7836577200000001</v>
       </c>
       <c r="N88">
-        <v>-0.6716501600000002</v>
+        <v>-0.6806577200000002</v>
       </c>
       <c r="O88">
-        <v>-0.1276135304</v>
+        <v>-0.1293249668000001</v>
       </c>
       <c r="P88">
-        <v>-0.5440366296000002</v>
+        <v>-0.5513327532000002</v>
       </c>
       <c r="Q88">
-        <v>0.1249633703999998</v>
+        <v>0.1176672467999998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4662003730109806</v>
+        <v>0.4985388632425943</v>
       </c>
       <c r="T88">
-        <v>7.69978047020889</v>
+        <v>8.292071275609572</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02526301679199288</v>
+        <v>0.02497263728863664</v>
       </c>
       <c r="W88">
-        <v>0.2298429806404481</v>
+        <v>0.2299114521273395</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1329632462736468</v>
+        <v>0.1314349330980876</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2648330155723226</v>
+        <v>0.2667330155723226</v>
       </c>
       <c r="C89">
-        <v>-1.765131221434796</v>
+        <v>-1.814277232718411</v>
       </c>
       <c r="D89">
-        <v>1.558268778565205</v>
+        <v>1.547322767281589</v>
       </c>
       <c r="E89">
-        <v>3.1634</v>
+        <v>3.2016</v>
       </c>
       <c r="F89">
-        <v>3.3234</v>
+        <v>3.3616</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8573,37 +8573,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M89">
-        <v>0.7836577200000001</v>
+        <v>0.79266528</v>
       </c>
       <c r="N89">
-        <v>-0.6806577200000002</v>
+        <v>-0.6896652800000002</v>
       </c>
       <c r="O89">
-        <v>-0.1293249668000001</v>
+        <v>-0.1310364032</v>
       </c>
       <c r="P89">
-        <v>-0.5513327532000002</v>
+        <v>-0.5586288768000001</v>
       </c>
       <c r="Q89">
-        <v>0.1176672467999998</v>
+        <v>0.1103711232</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4985388632425943</v>
+        <v>0.5362671018461439</v>
       </c>
       <c r="T89">
-        <v>8.292071275609572</v>
+        <v>8.983077215243705</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02497263728863664</v>
+        <v>0.02468885731944759</v>
       </c>
       <c r="W89">
-        <v>0.2299114521273395</v>
+        <v>0.2299783674440743</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1314349330980876</v>
+        <v>0.129941354312882</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2667330155723226</v>
+        <v>0.2686330155723227</v>
       </c>
       <c r="C90">
-        <v>-1.814277232718411</v>
+        <v>-1.863270536847091</v>
       </c>
       <c r="D90">
-        <v>1.547322767281589</v>
+        <v>1.536529463152909</v>
       </c>
       <c r="E90">
-        <v>3.2016</v>
+        <v>3.2398</v>
       </c>
       <c r="F90">
-        <v>3.3616</v>
+        <v>3.3998</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8655,37 +8655,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M90">
-        <v>0.79266528</v>
+        <v>0.8016728400000002</v>
       </c>
       <c r="N90">
-        <v>-0.6896652800000002</v>
+        <v>-0.6986728400000003</v>
       </c>
       <c r="O90">
-        <v>-0.1310364032</v>
+        <v>-0.1327478396000001</v>
       </c>
       <c r="P90">
-        <v>-0.5586288768000001</v>
+        <v>-0.5659250004000003</v>
       </c>
       <c r="Q90">
-        <v>0.1103711232</v>
+        <v>0.1030749995999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5362671018461439</v>
+        <v>0.5808550201957934</v>
       </c>
       <c r="T90">
-        <v>8.983077215243705</v>
+        <v>9.79972059844768</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02468885731944759</v>
+        <v>0.02441145442821784</v>
       </c>
       <c r="W90">
-        <v>0.2299783674440743</v>
+        <v>0.2300437790458263</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.129941354312882</v>
+        <v>0.1284813390958833</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2686330155723227</v>
+        <v>0.2705330155723226</v>
       </c>
       <c r="C91">
-        <v>-1.863270536847091</v>
+        <v>-1.912114307297051</v>
       </c>
       <c r="D91">
-        <v>1.536529463152909</v>
+        <v>1.525885692702949</v>
       </c>
       <c r="E91">
-        <v>3.2398</v>
+        <v>3.278</v>
       </c>
       <c r="F91">
-        <v>3.3998</v>
+        <v>3.438</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8737,37 +8737,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M91">
-        <v>0.8016728400000002</v>
+        <v>0.8106804000000001</v>
       </c>
       <c r="N91">
-        <v>-0.6986728400000003</v>
+        <v>-0.7076804000000002</v>
       </c>
       <c r="O91">
-        <v>-0.1327478396000001</v>
+        <v>-0.134459276</v>
       </c>
       <c r="P91">
-        <v>-0.5659250004000003</v>
+        <v>-0.5732211240000001</v>
       </c>
       <c r="Q91">
-        <v>0.1030749995999998</v>
+        <v>0.0957788759999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5808550201957934</v>
+        <v>0.6343605222153729</v>
       </c>
       <c r="T91">
-        <v>9.79972059844768</v>
+        <v>10.77969265829245</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02441145442821784</v>
+        <v>0.02414021604568209</v>
       </c>
       <c r="W91">
-        <v>0.2300437790458263</v>
+        <v>0.2301077370564282</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1284813390958833</v>
+        <v>0.1270537686614847</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2705330155723226</v>
+        <v>0.2724330155723226</v>
       </c>
       <c r="C92">
-        <v>-1.912114307297051</v>
+        <v>-1.960811630216858</v>
       </c>
       <c r="D92">
-        <v>1.525885692702949</v>
+        <v>1.515388369783143</v>
       </c>
       <c r="E92">
-        <v>3.278</v>
+        <v>3.3162</v>
       </c>
       <c r="F92">
-        <v>3.438</v>
+        <v>3.4762</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8819,37 +8819,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M92">
-        <v>0.8106804000000001</v>
+        <v>0.8196879600000001</v>
       </c>
       <c r="N92">
-        <v>-0.7076804000000002</v>
+        <v>-0.7166879600000002</v>
       </c>
       <c r="O92">
-        <v>-0.134459276</v>
+        <v>-0.1361707124</v>
       </c>
       <c r="P92">
-        <v>-0.5732211240000001</v>
+        <v>-0.5805172476000002</v>
       </c>
       <c r="Q92">
-        <v>0.0957788759999999</v>
+        <v>0.08848275239999981</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6343605222153729</v>
+        <v>0.6997561357948586</v>
       </c>
       <c r="T92">
-        <v>10.77969265829245</v>
+        <v>11.97743628699161</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02414021604568209</v>
+        <v>0.02387493894627899</v>
       </c>
       <c r="W92">
-        <v>0.2301077370564282</v>
+        <v>0.2301702893964674</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1270537686614847</v>
+        <v>0.1256575734014683</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2724330155723226</v>
+        <v>0.2743330155723226</v>
       </c>
       <c r="C93">
-        <v>-1.960811630216858</v>
+        <v>-2.009365507410745</v>
       </c>
       <c r="D93">
-        <v>1.515388369783143</v>
+        <v>1.505034492589255</v>
       </c>
       <c r="E93">
-        <v>3.3162</v>
+        <v>3.3544</v>
       </c>
       <c r="F93">
-        <v>3.4762</v>
+        <v>3.514400000000001</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8901,37 +8901,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M93">
-        <v>0.8196879600000001</v>
+        <v>0.8286955200000001</v>
       </c>
       <c r="N93">
-        <v>-0.7166879600000002</v>
+        <v>-0.7256955200000003</v>
       </c>
       <c r="O93">
-        <v>-0.1361707124</v>
+        <v>-0.1378821488</v>
       </c>
       <c r="P93">
-        <v>-0.5805172476000002</v>
+        <v>-0.5878133712000002</v>
       </c>
       <c r="Q93">
-        <v>0.08848275239999981</v>
+        <v>0.08118662879999983</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6997561357948586</v>
+        <v>0.7815006527692162</v>
       </c>
       <c r="T93">
-        <v>11.97743628699161</v>
+        <v>13.47461582286556</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02387493894627899</v>
+        <v>0.02361542874034117</v>
       </c>
       <c r="W93">
-        <v>0.2301702893964674</v>
+        <v>0.2302314819030276</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1256575734014683</v>
+        <v>0.124291730212322</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2743330155723226</v>
+        <v>0.2762330155723226</v>
       </c>
       <c r="C94">
-        <v>-2.009365507410745</v>
+        <v>-2.057778859200478</v>
       </c>
       <c r="D94">
-        <v>1.505034492589255</v>
+        <v>1.494821140799523</v>
       </c>
       <c r="E94">
-        <v>3.3544</v>
+        <v>3.3926</v>
       </c>
       <c r="F94">
-        <v>3.514400000000001</v>
+        <v>3.5526</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8983,37 +8983,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M94">
-        <v>0.8286955200000001</v>
+        <v>0.8377030800000002</v>
       </c>
       <c r="N94">
-        <v>-0.7256955200000003</v>
+        <v>-0.7347030800000003</v>
       </c>
       <c r="O94">
-        <v>-0.1378821488</v>
+        <v>-0.1395935852000001</v>
       </c>
       <c r="P94">
-        <v>-0.5878133712000002</v>
+        <v>-0.5951094948000002</v>
       </c>
       <c r="Q94">
-        <v>0.08118662879999983</v>
+        <v>0.07389050519999985</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7815006527692162</v>
+        <v>0.8866007460219615</v>
       </c>
       <c r="T94">
-        <v>13.47461582286556</v>
+        <v>15.39956094041779</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02361542874034117</v>
+        <v>0.02336149939904718</v>
       </c>
       <c r="W94">
-        <v>0.2302314819030276</v>
+        <v>0.2302913584417047</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.124291730212322</v>
+        <v>0.1229552599949851</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2762330155723226</v>
+        <v>0.2781330155723226</v>
       </c>
       <c r="C95">
-        <v>-2.057778859200478</v>
+        <v>-2.106054527171463</v>
       </c>
       <c r="D95">
-        <v>1.494821140799523</v>
+        <v>1.484745472828537</v>
       </c>
       <c r="E95">
-        <v>3.3926</v>
+        <v>3.430800000000001</v>
       </c>
       <c r="F95">
-        <v>3.5526</v>
+        <v>3.590800000000001</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9065,37 +9065,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M95">
-        <v>0.8377030800000002</v>
+        <v>0.8467106400000002</v>
       </c>
       <c r="N95">
-        <v>-0.7347030800000003</v>
+        <v>-0.7437106400000003</v>
       </c>
       <c r="O95">
-        <v>-0.1395935852000001</v>
+        <v>-0.1413050216000001</v>
       </c>
       <c r="P95">
-        <v>-0.5951094948000002</v>
+        <v>-0.6024056184000003</v>
       </c>
       <c r="Q95">
-        <v>0.07389050519999985</v>
+        <v>0.06659438159999975</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8866007460219615</v>
+        <v>1.026734203692289</v>
       </c>
       <c r="T95">
-        <v>15.39956094041779</v>
+        <v>17.96615443048742</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02336149939904718</v>
+        <v>0.02311297280969562</v>
       </c>
       <c r="W95">
-        <v>0.2302913584417047</v>
+        <v>0.2303499610114738</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1229552599949851</v>
+        <v>0.1216472253141875</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2781330155723226</v>
+        <v>0.2800330155723226</v>
       </c>
       <c r="C96">
-        <v>-2.106054527171463</v>
+        <v>-2.154195276808554</v>
       </c>
       <c r="D96">
-        <v>1.484745472828537</v>
+        <v>1.474804723191446</v>
       </c>
       <c r="E96">
-        <v>3.430800000000001</v>
+        <v>3.469</v>
       </c>
       <c r="F96">
-        <v>3.590800000000001</v>
+        <v>3.629</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9147,37 +9147,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M96">
-        <v>0.8467106400000002</v>
+        <v>0.8557182000000001</v>
       </c>
       <c r="N96">
-        <v>-0.7437106400000003</v>
+        <v>-0.7527182000000002</v>
       </c>
       <c r="O96">
-        <v>-0.1413050216000001</v>
+        <v>-0.143016458</v>
       </c>
       <c r="P96">
-        <v>-0.6024056184000003</v>
+        <v>-0.6097017420000002</v>
       </c>
       <c r="Q96">
-        <v>0.06659438159999975</v>
+        <v>0.05929825799999988</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.026734203692289</v>
+        <v>1.222921044430747</v>
       </c>
       <c r="T96">
-        <v>17.96615443048742</v>
+        <v>21.55938531658492</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02311297280969562</v>
+        <v>0.02286967835906724</v>
       </c>
       <c r="W96">
-        <v>0.2303499610114738</v>
+        <v>0.2304073298429319</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1216472253141875</v>
+        <v>0.120366728205617</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2800330155723226</v>
+        <v>0.2819330155723226</v>
       </c>
       <c r="C97">
-        <v>-2.154195276808554</v>
+        <v>-2.202203800026666</v>
       </c>
       <c r="D97">
-        <v>1.474804723191446</v>
+        <v>1.464996199973335</v>
       </c>
       <c r="E97">
-        <v>3.469</v>
+        <v>3.507200000000001</v>
       </c>
       <c r="F97">
-        <v>3.629</v>
+        <v>3.667200000000001</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9229,37 +9229,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M97">
-        <v>0.8557182000000001</v>
+        <v>0.8647257600000002</v>
       </c>
       <c r="N97">
-        <v>-0.7527182000000002</v>
+        <v>-0.7617257600000004</v>
       </c>
       <c r="O97">
-        <v>-0.143016458</v>
+        <v>-0.1447278944000001</v>
       </c>
       <c r="P97">
-        <v>-0.6097017420000002</v>
+        <v>-0.6169978656000003</v>
       </c>
       <c r="Q97">
-        <v>0.05929825799999988</v>
+        <v>0.05200213439999979</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.222921044430747</v>
+        <v>1.517201305538435</v>
       </c>
       <c r="T97">
-        <v>21.55938531658492</v>
+        <v>26.94923164573116</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02286967835906724</v>
+        <v>0.02263145254282695</v>
       </c>
       <c r="W97">
-        <v>0.2304073298429319</v>
+        <v>0.2304635034904014</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.120366728205617</v>
+        <v>0.1191129081201419</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2819330155723226</v>
+        <v>0.2838330155723226</v>
       </c>
       <c r="C98">
-        <v>-2.202203800026666</v>
+        <v>-2.250082717601081</v>
       </c>
       <c r="D98">
-        <v>1.464996199973335</v>
+        <v>1.455317282398919</v>
       </c>
       <c r="E98">
-        <v>3.5072</v>
+        <v>3.5454</v>
       </c>
       <c r="F98">
-        <v>3.6672</v>
+        <v>3.7054</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9311,37 +9311,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M98">
-        <v>0.8647257600000001</v>
+        <v>0.87373332</v>
       </c>
       <c r="N98">
-        <v>-0.7617257600000003</v>
+        <v>-0.7707333200000002</v>
       </c>
       <c r="O98">
-        <v>-0.1447278944000001</v>
+        <v>-0.1464393308</v>
       </c>
       <c r="P98">
-        <v>-0.6169978656000001</v>
+        <v>-0.6242939892000001</v>
       </c>
       <c r="Q98">
-        <v>0.0520021343999999</v>
+        <v>0.04470601079999992</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.517201305538431</v>
+        <v>2.007668407384574</v>
       </c>
       <c r="T98">
-        <v>26.94923164573109</v>
+        <v>35.93230886097479</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02263145254282696</v>
+        <v>0.02239813859908647</v>
       </c>
       <c r="W98">
-        <v>0.2304635034904014</v>
+        <v>0.2305185189183354</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1191129081201419</v>
+        <v>0.117884939995192</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2838330155723226</v>
+        <v>0.2857330155723226</v>
       </c>
       <c r="C99">
-        <v>-2.250082717601081</v>
+        <v>-2.29783458150205</v>
       </c>
       <c r="D99">
-        <v>1.455317282398919</v>
+        <v>1.44576541849795</v>
       </c>
       <c r="E99">
-        <v>3.5454</v>
+        <v>3.5836</v>
       </c>
       <c r="F99">
-        <v>3.7054</v>
+        <v>3.7436</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9393,37 +9393,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M99">
-        <v>0.87373332</v>
+        <v>0.8827408800000001</v>
       </c>
       <c r="N99">
-        <v>-0.7707333200000002</v>
+        <v>-0.7797408800000002</v>
       </c>
       <c r="O99">
-        <v>-0.1464393308</v>
+        <v>-0.1481507672</v>
       </c>
       <c r="P99">
-        <v>-0.6242939892000001</v>
+        <v>-0.6315901128000001</v>
       </c>
       <c r="Q99">
-        <v>0.04470601079999992</v>
+        <v>0.03740988719999994</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.007668407384574</v>
+        <v>2.988602611076861</v>
       </c>
       <c r="T99">
-        <v>35.93230886097479</v>
+        <v>53.89846329146218</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02239813859908647</v>
+        <v>0.02216958616440192</v>
       </c>
       <c r="W99">
-        <v>0.2305185189183354</v>
+        <v>0.2305724115824341</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.117884939995192</v>
+        <v>0.1166820324442206</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2857330155723226</v>
+        <v>0.2876330155723226</v>
       </c>
       <c r="C100">
-        <v>-2.29783458150205</v>
+        <v>-2.345461877138047</v>
       </c>
       <c r="D100">
-        <v>1.44576541849795</v>
+        <v>1.436338122861953</v>
       </c>
       <c r="E100">
-        <v>3.5836</v>
+        <v>3.6218</v>
       </c>
       <c r="F100">
-        <v>3.7436</v>
+        <v>3.7818</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9475,37 +9475,37 @@
         <v>0.1029999999999999</v>
       </c>
       <c r="M100">
-        <v>0.8827408800000001</v>
+        <v>0.8917484400000001</v>
       </c>
       <c r="N100">
-        <v>-0.7797408800000002</v>
+        <v>-0.7887484400000002</v>
       </c>
       <c r="O100">
-        <v>-0.1481507672</v>
+        <v>-0.1498622036</v>
       </c>
       <c r="P100">
-        <v>-0.6315901128000001</v>
+        <v>-0.6388862364000002</v>
       </c>
       <c r="Q100">
-        <v>0.03740988719999994</v>
+        <v>0.03011376359999984</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.988602611076861</v>
+        <v>5.931405222153722</v>
       </c>
       <c r="T100">
-        <v>53.89846329146218</v>
+        <v>107.7969265829244</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02216958616440192</v>
+        <v>0.02194565095062008</v>
       </c>
       <c r="W100">
-        <v>0.2305724115824341</v>
+        <v>0.2306252155058438</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1166820324442206</v>
+        <v>0.1155034260558951</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2876330155723226</v>
-      </c>
-      <c r="C101">
-        <v>-2.345461877138047</v>
-      </c>
-      <c r="D101">
-        <v>1.436338122861953</v>
-      </c>
-      <c r="E101">
-        <v>3.6218</v>
-      </c>
-      <c r="F101">
-        <v>3.7818</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>3.66</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.669</v>
-      </c>
-      <c r="L101">
-        <v>0.1029999999999999</v>
-      </c>
-      <c r="M101">
-        <v>0.8917484400000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.7887484400000002</v>
-      </c>
-      <c r="O101">
-        <v>-0.1498622036</v>
-      </c>
-      <c r="P101">
-        <v>-0.6388862364000002</v>
-      </c>
-      <c r="Q101">
-        <v>0.03011376359999984</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.931405222153722</v>
-      </c>
-      <c r="T101">
-        <v>107.7969265829244</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02194565095062008</v>
-      </c>
-      <c r="W101">
-        <v>0.2306252155058438</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1155034260558951</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
